--- a/mfcc_features_avg.xlsx
+++ b/mfcc_features_avg.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,47 +512,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-97.66531372070312</v>
+        <v>-71.8040771484375</v>
       </c>
       <c r="B2" t="n">
-        <v>195.4886016845703</v>
+        <v>112.2355728149414</v>
       </c>
       <c r="C2" t="n">
-        <v>-30.90135765075684</v>
+        <v>-15.18389797210693</v>
       </c>
       <c r="D2" t="n">
-        <v>26.08112144470215</v>
+        <v>23.55993270874023</v>
       </c>
       <c r="E2" t="n">
-        <v>32.53065872192383</v>
+        <v>6.407943248748779</v>
       </c>
       <c r="F2" t="n">
-        <v>3.308772325515747</v>
+        <v>-20.31331253051758</v>
       </c>
       <c r="G2" t="n">
-        <v>-23.95533180236816</v>
+        <v>-1.966050028800964</v>
       </c>
       <c r="H2" t="n">
-        <v>16.03118896484375</v>
+        <v>-13.93924522399902</v>
       </c>
       <c r="I2" t="n">
-        <v>-36.1404914855957</v>
+        <v>14.22094058990479</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.882914066314697</v>
+        <v>6.74221134185791</v>
       </c>
       <c r="K2" t="n">
-        <v>13.02513980865479</v>
+        <v>2.716077089309692</v>
       </c>
       <c r="L2" t="n">
-        <v>-31.64862251281738</v>
+        <v>-6.647804260253906</v>
       </c>
       <c r="M2" t="n">
-        <v>-22.4039478302002</v>
+        <v>-0.6647546291351318</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Left Mariana.m4a</t>
+          <t>Left Joel.wav</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -562,53 +562,53 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-121.9282836914062</v>
+        <v>-106.4817657470703</v>
       </c>
       <c r="B3" t="n">
-        <v>154.7428131103516</v>
+        <v>128.2368621826172</v>
       </c>
       <c r="C3" t="n">
-        <v>-25.40764617919922</v>
+        <v>-22.19016647338867</v>
       </c>
       <c r="D3" t="n">
-        <v>55.98431396484375</v>
+        <v>18.16694068908691</v>
       </c>
       <c r="E3" t="n">
-        <v>9.994221687316895</v>
+        <v>3.970492124557495</v>
       </c>
       <c r="F3" t="n">
-        <v>18.7534122467041</v>
+        <v>-19.33951950073242</v>
       </c>
       <c r="G3" t="n">
-        <v>-22.82929992675781</v>
+        <v>-3.238811016082764</v>
       </c>
       <c r="H3" t="n">
-        <v>3.153623342514038</v>
+        <v>-5.847513198852539</v>
       </c>
       <c r="I3" t="n">
-        <v>-21.19968605041504</v>
+        <v>10.98017120361328</v>
       </c>
       <c r="J3" t="n">
-        <v>-15.21120929718018</v>
+        <v>6.029256820678711</v>
       </c>
       <c r="K3" t="n">
-        <v>-19.11922454833984</v>
+        <v>-0.01313424110412598</v>
       </c>
       <c r="L3" t="n">
-        <v>-6.237063884735107</v>
+        <v>-0.6434212923049927</v>
       </c>
       <c r="M3" t="n">
-        <v>-13.73203754425049</v>
+        <v>3.959981203079224</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Left1 Mariana.m4a</t>
+          <t>Left1 Joel.wav</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -618,53 +618,53 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-58.5460205078125</v>
+        <v>-103.7057723999023</v>
       </c>
       <c r="B4" t="n">
-        <v>172.9784393310547</v>
+        <v>107.1809921264648</v>
       </c>
       <c r="C4" t="n">
-        <v>-37.97485733032227</v>
+        <v>-4.075252056121826</v>
       </c>
       <c r="D4" t="n">
-        <v>44.09109497070312</v>
+        <v>17.16353988647461</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.473976135253906</v>
+        <v>8.966035842895508</v>
       </c>
       <c r="F4" t="n">
-        <v>16.35755348205566</v>
+        <v>-15.49599266052246</v>
       </c>
       <c r="G4" t="n">
-        <v>-33.31392288208008</v>
+        <v>-4.93409252166748</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.115351676940918</v>
+        <v>-11.3892822265625</v>
       </c>
       <c r="I4" t="n">
-        <v>-17.86356544494629</v>
+        <v>4.68236255645752</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.965139389038086</v>
+        <v>4.859355449676514</v>
       </c>
       <c r="K4" t="n">
-        <v>-16.85312461853027</v>
+        <v>1.647185087203979</v>
       </c>
       <c r="L4" t="n">
-        <v>3.499408006668091</v>
+        <v>6.217882633209229</v>
       </c>
       <c r="M4" t="n">
-        <v>-21.1377124786377</v>
+        <v>1.953668832778931</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Left10 Mariana.m4a</t>
+          <t>Left2 Joel.wav</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -674,53 +674,53 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-146.3861083984375</v>
+        <v>-76.4688720703125</v>
       </c>
       <c r="B5" t="n">
-        <v>154.068359375</v>
+        <v>122.8817749023438</v>
       </c>
       <c r="C5" t="n">
-        <v>-15.58481216430664</v>
+        <v>-18.81569671630859</v>
       </c>
       <c r="D5" t="n">
-        <v>55.23648452758789</v>
+        <v>18.7939281463623</v>
       </c>
       <c r="E5" t="n">
-        <v>10.62781143188477</v>
+        <v>6.611835479736328</v>
       </c>
       <c r="F5" t="n">
-        <v>24.00423240661621</v>
+        <v>-17.07516098022461</v>
       </c>
       <c r="G5" t="n">
-        <v>-13.52423095703125</v>
+        <v>0.15595743060112</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.717081069946289</v>
+        <v>-10.1917552947998</v>
       </c>
       <c r="I5" t="n">
-        <v>-28.50242614746094</v>
+        <v>1.33712100982666</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.259363174438477</v>
+        <v>1.215933561325073</v>
       </c>
       <c r="K5" t="n">
-        <v>-14.42453384399414</v>
+        <v>-0.4178054332733154</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3819439709186554</v>
+        <v>3.551511287689209</v>
       </c>
       <c r="M5" t="n">
-        <v>-14.73240375518799</v>
+        <v>3.748766899108887</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Left2 Mariana.m4a</t>
+          <t>Left3 Joel.wav</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -730,53 +730,53 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-95.04987335205078</v>
+        <v>-91.39448547363281</v>
       </c>
       <c r="B6" t="n">
-        <v>164.9542083740234</v>
+        <v>117.1110687255859</v>
       </c>
       <c r="C6" t="n">
-        <v>-21.56991386413574</v>
+        <v>-14.32407474517822</v>
       </c>
       <c r="D6" t="n">
-        <v>43.88999557495117</v>
+        <v>19.93028831481934</v>
       </c>
       <c r="E6" t="n">
-        <v>10.04514312744141</v>
+        <v>9.125797271728516</v>
       </c>
       <c r="F6" t="n">
-        <v>10.06138324737549</v>
+        <v>-23.57026863098145</v>
       </c>
       <c r="G6" t="n">
-        <v>-11.47116470336914</v>
+        <v>-2.121702909469604</v>
       </c>
       <c r="H6" t="n">
-        <v>-17.42646980285645</v>
+        <v>-11.53048324584961</v>
       </c>
       <c r="I6" t="n">
-        <v>-23.38273048400879</v>
+        <v>13.14991664886475</v>
       </c>
       <c r="J6" t="n">
-        <v>-24.06075096130371</v>
+        <v>7.004104614257812</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.593727111816406</v>
+        <v>-4.109302520751953</v>
       </c>
       <c r="L6" t="n">
-        <v>2.172616243362427</v>
+        <v>-3.072667360305786</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.61394882202148</v>
+        <v>0.9757453203201294</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Left3 Mariana.m4a</t>
+          <t>Left4 Joel.wav</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -786,53 +786,53 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-122.3967666625977</v>
+        <v>-71.15321350097656</v>
       </c>
       <c r="B7" t="n">
-        <v>169.3599548339844</v>
+        <v>113.1995849609375</v>
       </c>
       <c r="C7" t="n">
-        <v>-16.16336250305176</v>
+        <v>-20.76276206970215</v>
       </c>
       <c r="D7" t="n">
-        <v>45.56935501098633</v>
+        <v>23.36148071289062</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8913056254386902</v>
+        <v>1.79542350769043</v>
       </c>
       <c r="F7" t="n">
-        <v>19.62103652954102</v>
+        <v>-19.34828758239746</v>
       </c>
       <c r="G7" t="n">
-        <v>-15.20732593536377</v>
+        <v>0.5174171328544617</v>
       </c>
       <c r="H7" t="n">
-        <v>0.216082975268364</v>
+        <v>-12.81495571136475</v>
       </c>
       <c r="I7" t="n">
-        <v>-25.78052711486816</v>
+        <v>12.90143775939941</v>
       </c>
       <c r="J7" t="n">
-        <v>-9.247923851013184</v>
+        <v>5.956028938293457</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.41268634796143</v>
+        <v>-3.634991407394409</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.116288065910339</v>
+        <v>0.6303516626358032</v>
       </c>
       <c r="M7" t="n">
-        <v>-14.12213611602783</v>
+        <v>-0.2651865482330322</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Left4 Mariana.m4a</t>
+          <t>Left5 Joel.wav</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -842,53 +842,53 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-80.601806640625</v>
+        <v>-99.24075317382812</v>
       </c>
       <c r="B8" t="n">
-        <v>131.1949462890625</v>
+        <v>109.6936950683594</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.19675350189209</v>
+        <v>-12.60856056213379</v>
       </c>
       <c r="D8" t="n">
-        <v>62.1141471862793</v>
+        <v>20.93209075927734</v>
       </c>
       <c r="E8" t="n">
-        <v>1.712486147880554</v>
+        <v>2.566448211669922</v>
       </c>
       <c r="F8" t="n">
-        <v>20.61079216003418</v>
+        <v>-15.27226829528809</v>
       </c>
       <c r="G8" t="n">
-        <v>-16.45305442810059</v>
+        <v>-0.6308063864707947</v>
       </c>
       <c r="H8" t="n">
-        <v>1.910090565681458</v>
+        <v>-9.565656661987305</v>
       </c>
       <c r="I8" t="n">
-        <v>-36.73734664916992</v>
+        <v>12.68030166625977</v>
       </c>
       <c r="J8" t="n">
-        <v>-14.19137096405029</v>
+        <v>4.734650135040283</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.013617515563965</v>
+        <v>-3.260698318481445</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.245809197425842</v>
+        <v>3.905904769897461</v>
       </c>
       <c r="M8" t="n">
-        <v>-26.16232299804688</v>
+        <v>-1.410958290100098</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Left5 Mariana.m4a</t>
+          <t>Left6 Joel.wav</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -898,53 +898,53 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-107.7187118530273</v>
+        <v>-21.45622253417969</v>
       </c>
       <c r="B9" t="n">
-        <v>179.6306762695312</v>
+        <v>89.19442749023438</v>
       </c>
       <c r="C9" t="n">
-        <v>-22.02877807617188</v>
+        <v>-34.8651008605957</v>
       </c>
       <c r="D9" t="n">
-        <v>43.07976150512695</v>
+        <v>17.43874168395996</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5717554092407227</v>
+        <v>6.898602485656738</v>
       </c>
       <c r="F9" t="n">
-        <v>7.440617084503174</v>
+        <v>-16.25429344177246</v>
       </c>
       <c r="G9" t="n">
-        <v>-11.25882244110107</v>
+        <v>10.77474594116211</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.474796533584595</v>
+        <v>-28.14611053466797</v>
       </c>
       <c r="I9" t="n">
-        <v>-24.85915184020996</v>
+        <v>-4.318309307098389</v>
       </c>
       <c r="J9" t="n">
-        <v>-13.26090145111084</v>
+        <v>2.452599763870239</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.82264709472656</v>
+        <v>4.60897970199585</v>
       </c>
       <c r="L9" t="n">
-        <v>1.764656901359558</v>
+        <v>9.009366989135742</v>
       </c>
       <c r="M9" t="n">
-        <v>-7.897720336914062</v>
+        <v>-9.263223648071289</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Left6 Mariana.m4a</t>
+          <t>Left7 Joel.wav</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -954,53 +954,53 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-119.9653549194336</v>
+        <v>-85.11765289306641</v>
       </c>
       <c r="B10" t="n">
-        <v>156.6995697021484</v>
+        <v>119.8439407348633</v>
       </c>
       <c r="C10" t="n">
-        <v>-32.44696044921875</v>
+        <v>-23.95764923095703</v>
       </c>
       <c r="D10" t="n">
-        <v>53.31327819824219</v>
+        <v>28.55070495605469</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.603991985321045</v>
+        <v>0.7691645622253418</v>
       </c>
       <c r="F10" t="n">
-        <v>24.93677711486816</v>
+        <v>-29.41290092468262</v>
       </c>
       <c r="G10" t="n">
-        <v>-20.63986778259277</v>
+        <v>-1.710836410522461</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.525088787078857</v>
+        <v>-14.48098850250244</v>
       </c>
       <c r="I10" t="n">
-        <v>-36.99448776245117</v>
+        <v>4.668339729309082</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.170034408569336</v>
+        <v>3.02626371383667</v>
       </c>
       <c r="K10" t="n">
-        <v>-11.18080139160156</v>
+        <v>2.576141834259033</v>
       </c>
       <c r="L10" t="n">
-        <v>3.310575485229492</v>
+        <v>-0.2306655943393707</v>
       </c>
       <c r="M10" t="n">
-        <v>-15.13488101959229</v>
+        <v>0.5871131420135498</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Left7 Mariana.m4a</t>
+          <t>Left8 Joel.wav</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1010,53 +1010,53 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-46.54286575317383</v>
+        <v>-40.19889068603516</v>
       </c>
       <c r="B11" t="n">
-        <v>160.8977508544922</v>
+        <v>87.49761962890625</v>
       </c>
       <c r="C11" t="n">
-        <v>-41.89723587036133</v>
+        <v>-22.050537109375</v>
       </c>
       <c r="D11" t="n">
-        <v>51.32638549804688</v>
+        <v>28.09512710571289</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.88359832763672</v>
+        <v>0.1879253387451172</v>
       </c>
       <c r="F11" t="n">
-        <v>5.993506908416748</v>
+        <v>-24.82884407043457</v>
       </c>
       <c r="G11" t="n">
-        <v>-20.11401176452637</v>
+        <v>9.162453651428223</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.375423431396484</v>
+        <v>-20.43125534057617</v>
       </c>
       <c r="I11" t="n">
-        <v>-9.957304954528809</v>
+        <v>6.291667461395264</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.00998401641846</v>
+        <v>4.021479606628418</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.674105644226074</v>
+        <v>5.579592704772949</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.685297727584839</v>
+        <v>3.013643503189087</v>
       </c>
       <c r="M11" t="n">
-        <v>-17.01767539978027</v>
+        <v>-4.998010635375977</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Left8 Mariana.m4a</t>
+          <t>Left9 Joel.wav</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1066,109 +1066,109 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-77.45549774169922</v>
+        <v>-36.17762756347656</v>
       </c>
       <c r="B12" t="n">
-        <v>159.6003265380859</v>
+        <v>102.3365631103516</v>
       </c>
       <c r="C12" t="n">
-        <v>-15.864990234375</v>
+        <v>-32.84944152832031</v>
       </c>
       <c r="D12" t="n">
-        <v>49.68521499633789</v>
+        <v>27.28002738952637</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.62670421600342</v>
+        <v>-13.61792182922363</v>
       </c>
       <c r="F12" t="n">
-        <v>12.85367202758789</v>
+        <v>-23.15808868408203</v>
       </c>
       <c r="G12" t="n">
-        <v>-25.38862609863281</v>
+        <v>6.84476375579834</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9156929850578308</v>
+        <v>-20.80265808105469</v>
       </c>
       <c r="I12" t="n">
-        <v>-32.15521621704102</v>
+        <v>3.684324264526367</v>
       </c>
       <c r="J12" t="n">
-        <v>-9.267360687255859</v>
+        <v>4.195711135864258</v>
       </c>
       <c r="K12" t="n">
-        <v>-16.30611228942871</v>
+        <v>-2.741775035858154</v>
       </c>
       <c r="L12" t="n">
-        <v>4.947212696075439</v>
+        <v>6.893524169921875</v>
       </c>
       <c r="M12" t="n">
-        <v>-11.84476566314697</v>
+        <v>-11.38441371917725</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Left9 Mariana.m4a</t>
+          <t>Right Joel.wav</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>LEFT</t>
+          <t>RIGHT</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-184.786376953125</v>
+        <v>-80.72531890869141</v>
       </c>
       <c r="B13" t="n">
-        <v>230.7789764404297</v>
+        <v>135.9575653076172</v>
       </c>
       <c r="C13" t="n">
-        <v>11.89828014373779</v>
+        <v>-39.11029052734375</v>
       </c>
       <c r="D13" t="n">
-        <v>-34.08364486694336</v>
+        <v>22.55585479736328</v>
       </c>
       <c r="E13" t="n">
-        <v>-25.10171699523926</v>
+        <v>-8.825613021850586</v>
       </c>
       <c r="F13" t="n">
-        <v>17.06134796142578</v>
+        <v>-15.34232234954834</v>
       </c>
       <c r="G13" t="n">
-        <v>-28.76432228088379</v>
+        <v>5.528236865997314</v>
       </c>
       <c r="H13" t="n">
-        <v>26.55525779724121</v>
+        <v>-9.693671226501465</v>
       </c>
       <c r="I13" t="n">
-        <v>-26.03491020202637</v>
+        <v>3.221199512481689</v>
       </c>
       <c r="J13" t="n">
-        <v>-13.56418323516846</v>
+        <v>5.380485534667969</v>
       </c>
       <c r="K13" t="n">
-        <v>8.109940528869629</v>
+        <v>-2.094040632247925</v>
       </c>
       <c r="L13" t="n">
-        <v>-21.3316478729248</v>
+        <v>2.056243419647217</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.079259753227234</v>
+        <v>-7.438733100891113</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Right Mariana.m4a</t>
+          <t>Right1 Joel.wav</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1178,53 +1178,53 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-124.1233444213867</v>
+        <v>-79.23252868652344</v>
       </c>
       <c r="B14" t="n">
-        <v>180.7455291748047</v>
+        <v>119.6492462158203</v>
       </c>
       <c r="C14" t="n">
-        <v>-16.01513481140137</v>
+        <v>-23.7485408782959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.78322601318359</v>
+        <v>24.84591484069824</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.14900016784668</v>
+        <v>3.898741722106934</v>
       </c>
       <c r="F14" t="n">
-        <v>30.41635131835938</v>
+        <v>-16.84067535400391</v>
       </c>
       <c r="G14" t="n">
-        <v>-15.66291522979736</v>
+        <v>-1.225146293640137</v>
       </c>
       <c r="H14" t="n">
-        <v>2.164702177047729</v>
+        <v>-17.81306838989258</v>
       </c>
       <c r="I14" t="n">
-        <v>-33.15756607055664</v>
+        <v>8.971433639526367</v>
       </c>
       <c r="J14" t="n">
-        <v>-18.19907569885254</v>
+        <v>5.528022766113281</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.642646789550781</v>
+        <v>6.218060970306396</v>
       </c>
       <c r="L14" t="n">
-        <v>4.91999340057373</v>
+        <v>3.798705101013184</v>
       </c>
       <c r="M14" t="n">
-        <v>2.562643766403198</v>
+        <v>-12.11622142791748</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Right1 Mariana.m4a</t>
+          <t>Right2 Joel.wav</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1234,53 +1234,53 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-135.5034637451172</v>
+        <v>-55.82753753662109</v>
       </c>
       <c r="B15" t="n">
-        <v>187.6472778320312</v>
+        <v>147.913330078125</v>
       </c>
       <c r="C15" t="n">
-        <v>-23.24754333496094</v>
+        <v>-47.88676452636719</v>
       </c>
       <c r="D15" t="n">
-        <v>23.48468017578125</v>
+        <v>28.74621200561523</v>
       </c>
       <c r="E15" t="n">
-        <v>-24.69403076171875</v>
+        <v>-20.7788200378418</v>
       </c>
       <c r="F15" t="n">
-        <v>21.31327819824219</v>
+        <v>-7.838300228118896</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.506818771362305</v>
+        <v>-5.975383281707764</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.645981311798096</v>
+        <v>-19.19586944580078</v>
       </c>
       <c r="I15" t="n">
-        <v>-20.29250144958496</v>
+        <v>10.38313102722168</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.92712688446045</v>
+        <v>5.996101856231689</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.926681518554688</v>
+        <v>0.6702079772949219</v>
       </c>
       <c r="L15" t="n">
-        <v>8.207236289978027</v>
+        <v>-4.930113315582275</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.669203996658325</v>
+        <v>-14.33584117889404</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Right10 Mariana.m4a</t>
+          <t>Right3 Joel.wav</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1290,53 +1290,53 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-97.18242645263672</v>
+        <v>-34.40943145751953</v>
       </c>
       <c r="B16" t="n">
-        <v>193.572509765625</v>
+        <v>125.461311340332</v>
       </c>
       <c r="C16" t="n">
-        <v>-30.83052062988281</v>
+        <v>-33.67449951171875</v>
       </c>
       <c r="D16" t="n">
-        <v>34.46287536621094</v>
+        <v>24.15680885314941</v>
       </c>
       <c r="E16" t="n">
-        <v>-21.3944034576416</v>
+        <v>-8.128495216369629</v>
       </c>
       <c r="F16" t="n">
-        <v>19.69606971740723</v>
+        <v>-18.92547225952148</v>
       </c>
       <c r="G16" t="n">
-        <v>-11.10718059539795</v>
+        <v>-3.314825296401978</v>
       </c>
       <c r="H16" t="n">
-        <v>-8.473450660705566</v>
+        <v>-21.55322265625</v>
       </c>
       <c r="I16" t="n">
-        <v>-19.02849388122559</v>
+        <v>3.605244636535645</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.03984642028809</v>
+        <v>1.442545294761658</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.941370487213135</v>
+        <v>5.970919132232666</v>
       </c>
       <c r="L16" t="n">
-        <v>3.012140274047852</v>
+        <v>2.81083607673645</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.060831069946289</v>
+        <v>-9.476496696472168</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Right11 Mariana.m4a</t>
+          <t>Right4 Joel.wav</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1346,53 +1346,53 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-131.0364685058594</v>
+        <v>-6.993817329406738</v>
       </c>
       <c r="B17" t="n">
-        <v>176.3777313232422</v>
+        <v>108.9065246582031</v>
       </c>
       <c r="C17" t="n">
-        <v>-18.9588680267334</v>
+        <v>-36.20023727416992</v>
       </c>
       <c r="D17" t="n">
-        <v>33.59294509887695</v>
+        <v>24.03220558166504</v>
       </c>
       <c r="E17" t="n">
-        <v>-14.92722320556641</v>
+        <v>-7.378757476806641</v>
       </c>
       <c r="F17" t="n">
-        <v>24.42144203186035</v>
+        <v>-23.05855941772461</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.87509059906006</v>
+        <v>7.994312286376953</v>
       </c>
       <c r="H17" t="n">
-        <v>1.293593764305115</v>
+        <v>-18.47238731384277</v>
       </c>
       <c r="I17" t="n">
-        <v>-23.89893913269043</v>
+        <v>0.4232478141784668</v>
       </c>
       <c r="J17" t="n">
-        <v>-13.18116760253906</v>
+        <v>10.04016304016113</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.577192306518555</v>
+        <v>1.756926536560059</v>
       </c>
       <c r="L17" t="n">
-        <v>5.440061092376709</v>
+        <v>0.8715844750404358</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.854504108428955</v>
+        <v>-6.979316234588623</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Right2 Mariana.m4a</t>
+          <t>Right5 Joel.wav</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1402,53 +1402,53 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-109.6037368774414</v>
+        <v>-9.081676483154297</v>
       </c>
       <c r="B18" t="n">
-        <v>187.2379302978516</v>
+        <v>111.7480926513672</v>
       </c>
       <c r="C18" t="n">
-        <v>-28.92886352539062</v>
+        <v>-41.68596649169922</v>
       </c>
       <c r="D18" t="n">
-        <v>30.3832950592041</v>
+        <v>33.51227569580078</v>
       </c>
       <c r="E18" t="n">
-        <v>-35.07443618774414</v>
+        <v>-19.05681610107422</v>
       </c>
       <c r="F18" t="n">
-        <v>19.1688289642334</v>
+        <v>-19.36031341552734</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.31952953338623</v>
+        <v>7.203810691833496</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.514103889465332</v>
+        <v>-26.93455123901367</v>
       </c>
       <c r="I18" t="n">
-        <v>-23.72596740722656</v>
+        <v>6.800590515136719</v>
       </c>
       <c r="J18" t="n">
-        <v>-20.79589653015137</v>
+        <v>2.425358533859253</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.57075834274292</v>
+        <v>-5.798908233642578</v>
       </c>
       <c r="L18" t="n">
-        <v>14.08239269256592</v>
+        <v>3.931180477142334</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.422839522361755</v>
+        <v>-13.00066947937012</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Right3 Mariana.m4a</t>
+          <t>Right6 Joel.wav</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1458,53 +1458,53 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-129.1633605957031</v>
+        <v>-47.94475173950195</v>
       </c>
       <c r="B19" t="n">
-        <v>190.4566650390625</v>
+        <v>146.1143341064453</v>
       </c>
       <c r="C19" t="n">
-        <v>-27.83657836914062</v>
+        <v>-44.40506744384766</v>
       </c>
       <c r="D19" t="n">
-        <v>27.55708122253418</v>
+        <v>28.46457862854004</v>
       </c>
       <c r="E19" t="n">
-        <v>-25.42405128479004</v>
+        <v>-12.08392524719238</v>
       </c>
       <c r="F19" t="n">
-        <v>27.14810752868652</v>
+        <v>-11.94735145568848</v>
       </c>
       <c r="G19" t="n">
-        <v>-11.55721569061279</v>
+        <v>-0.3538424968719482</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.620019912719727</v>
+        <v>-12.44918823242188</v>
       </c>
       <c r="I19" t="n">
-        <v>-28.92043495178223</v>
+        <v>5.219233512878418</v>
       </c>
       <c r="J19" t="n">
-        <v>-18.6866283416748</v>
+        <v>6.861628532409668</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.135989189147949</v>
+        <v>-0.3248788118362427</v>
       </c>
       <c r="L19" t="n">
-        <v>10.69801712036133</v>
+        <v>-4.199848175048828</v>
       </c>
       <c r="M19" t="n">
-        <v>3.045474290847778</v>
+        <v>-4.561396598815918</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Right4 Mariana.m4a</t>
+          <t>Right7 Joel.wav</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1514,53 +1514,53 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-152.8065338134766</v>
+        <v>-47.77490615844727</v>
       </c>
       <c r="B20" t="n">
-        <v>195.879638671875</v>
+        <v>145.2520599365234</v>
       </c>
       <c r="C20" t="n">
-        <v>-27.84371948242188</v>
+        <v>-45.95113372802734</v>
       </c>
       <c r="D20" t="n">
-        <v>25.96476936340332</v>
+        <v>23.07193756103516</v>
       </c>
       <c r="E20" t="n">
-        <v>-26.42960548400879</v>
+        <v>-4.738007545471191</v>
       </c>
       <c r="F20" t="n">
-        <v>13.93912029266357</v>
+        <v>-16.92867088317871</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7835667729377747</v>
+        <v>-7.303942680358887</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.517281293869019</v>
+        <v>-15.76884651184082</v>
       </c>
       <c r="I20" t="n">
-        <v>-12.13179683685303</v>
+        <v>7.12506103515625</v>
       </c>
       <c r="J20" t="n">
-        <v>-19.14237976074219</v>
+        <v>4.324636936187744</v>
       </c>
       <c r="K20" t="n">
-        <v>-12.87168788909912</v>
+        <v>5.583824157714844</v>
       </c>
       <c r="L20" t="n">
-        <v>9.863654136657715</v>
+        <v>1.403789043426514</v>
       </c>
       <c r="M20" t="n">
-        <v>2.831142663955688</v>
+        <v>-4.889609336853027</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Right5 Mariana.m4a</t>
+          <t>Right8 Joel.wav</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1570,53 +1570,53 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-58.75426864624023</v>
+        <v>-27.54493141174316</v>
       </c>
       <c r="B21" t="n">
-        <v>199.1628875732422</v>
+        <v>107.6512298583984</v>
       </c>
       <c r="C21" t="n">
-        <v>-43.65609359741211</v>
+        <v>-27.08330154418945</v>
       </c>
       <c r="D21" t="n">
-        <v>26.38002014160156</v>
+        <v>30.29557609558105</v>
       </c>
       <c r="E21" t="n">
-        <v>-30.10581970214844</v>
+        <v>-7.876189231872559</v>
       </c>
       <c r="F21" t="n">
-        <v>16.79516792297363</v>
+        <v>-19.67034149169922</v>
       </c>
       <c r="G21" t="n">
-        <v>-16.96138572692871</v>
+        <v>5.259865760803223</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.545813083648682</v>
+        <v>-16.13751411437988</v>
       </c>
       <c r="I21" t="n">
-        <v>-19.42373847961426</v>
+        <v>-1.51975154876709</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.84431648254395</v>
+        <v>4.40333366394043</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.883077621459961</v>
+        <v>-6.193296909332275</v>
       </c>
       <c r="L21" t="n">
-        <v>3.734600067138672</v>
+        <v>-2.939731597900391</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.561832427978516</v>
+        <v>-8.13447380065918</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Right6 Mariana.m4a</t>
+          <t>Right9 Joel.wav</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1626,221 +1626,221 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-90.40061187744141</v>
+        <v>-20.38778686523438</v>
       </c>
       <c r="B22" t="n">
-        <v>177.1400604248047</v>
+        <v>123.7190017700195</v>
       </c>
       <c r="C22" t="n">
-        <v>-21.93411064147949</v>
+        <v>-15.45013523101807</v>
       </c>
       <c r="D22" t="n">
-        <v>38.16240310668945</v>
+        <v>22.37673950195312</v>
       </c>
       <c r="E22" t="n">
-        <v>-27.95257568359375</v>
+        <v>-22.64885520935059</v>
       </c>
       <c r="F22" t="n">
-        <v>15.24128437042236</v>
+        <v>1.150037050247192</v>
       </c>
       <c r="G22" t="n">
-        <v>-16.00951957702637</v>
+        <v>14.48337936401367</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.855190753936768</v>
+        <v>-11.15673828125</v>
       </c>
       <c r="I22" t="n">
-        <v>-17.00887107849121</v>
+        <v>4.912160873413086</v>
       </c>
       <c r="J22" t="n">
-        <v>-20.96757507324219</v>
+        <v>-0.6678223609924316</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.887779235839844</v>
+        <v>4.809696197509766</v>
       </c>
       <c r="L22" t="n">
-        <v>5.773562908172607</v>
+        <v>16.63393402099609</v>
       </c>
       <c r="M22" t="n">
-        <v>-10.94179248809814</v>
+        <v>-0.1311541795730591</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Right7 Mariana.m4a</t>
+          <t>Up Joel.wav</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>RIGHT</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-117.8413162231445</v>
+        <v>59.64924621582031</v>
       </c>
       <c r="B23" t="n">
-        <v>186.2340545654297</v>
+        <v>63.71730041503906</v>
       </c>
       <c r="C23" t="n">
-        <v>-10.29952526092529</v>
+        <v>-9.453037261962891</v>
       </c>
       <c r="D23" t="n">
-        <v>31.29184913635254</v>
+        <v>16.25179672241211</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.38059425354004</v>
+        <v>-7.258745193481445</v>
       </c>
       <c r="F23" t="n">
-        <v>19.37316131591797</v>
+        <v>0.6988469362258911</v>
       </c>
       <c r="G23" t="n">
-        <v>-15.8694543838501</v>
+        <v>12.63141632080078</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.430699348449707</v>
+        <v>-8.698083877563477</v>
       </c>
       <c r="I23" t="n">
-        <v>-24.85701560974121</v>
+        <v>-1.05882453918457</v>
       </c>
       <c r="J23" t="n">
-        <v>-21.39862632751465</v>
+        <v>4.653767585754395</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.229179382324219</v>
+        <v>4.478461265563965</v>
       </c>
       <c r="L23" t="n">
-        <v>4.554283142089844</v>
+        <v>7.599067687988281</v>
       </c>
       <c r="M23" t="n">
-        <v>-7.182525157928467</v>
+        <v>-8.336525917053223</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Right8 Mariana.m4a</t>
+          <t>Up1 Joel.wav</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>RIGHT</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-109.1428146362305</v>
+        <v>81.9110107421875</v>
       </c>
       <c r="B24" t="n">
-        <v>184.1938934326172</v>
+        <v>58.14257049560547</v>
       </c>
       <c r="C24" t="n">
-        <v>-19.37752342224121</v>
+        <v>-11.93302154541016</v>
       </c>
       <c r="D24" t="n">
-        <v>34.20302200317383</v>
+        <v>11.94034290313721</v>
       </c>
       <c r="E24" t="n">
-        <v>-28.06240081787109</v>
+        <v>-9.179166793823242</v>
       </c>
       <c r="F24" t="n">
-        <v>22.92333984375</v>
+        <v>-2.563315391540527</v>
       </c>
       <c r="G24" t="n">
-        <v>-15.91997146606445</v>
+        <v>3.054642915725708</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.006080627441406</v>
+        <v>-4.924272060394287</v>
       </c>
       <c r="I24" t="n">
-        <v>-18.0941219329834</v>
+        <v>1.986850023269653</v>
       </c>
       <c r="J24" t="n">
-        <v>-18.90976524353027</v>
+        <v>5.170926570892334</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.547192096710205</v>
+        <v>2.812670469284058</v>
       </c>
       <c r="L24" t="n">
-        <v>8.696247100830078</v>
+        <v>4.453874588012695</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.594837188720703</v>
+        <v>-4.136713027954102</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Right9 Mariana.m4a</t>
+          <t>Up2 Joel.wav</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>RIGHT</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-243.3732757568359</v>
+        <v>5.724708557128906</v>
       </c>
       <c r="B25" t="n">
-        <v>211.2006988525391</v>
+        <v>69.66585540771484</v>
       </c>
       <c r="C25" t="n">
-        <v>10.57912349700928</v>
+        <v>-5.289958953857422</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.23654174804688</v>
+        <v>21.78210830688477</v>
       </c>
       <c r="E25" t="n">
-        <v>-26.63302040100098</v>
+        <v>-12.24944877624512</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.19052600860596</v>
+        <v>-4.939773082733154</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.116551160812378</v>
+        <v>8.614442825317383</v>
       </c>
       <c r="H25" t="n">
-        <v>26.74766731262207</v>
+        <v>-8.361204147338867</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.221524715423584</v>
+        <v>8.281285285949707</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.31777286529541</v>
+        <v>-1.925089359283447</v>
       </c>
       <c r="K25" t="n">
-        <v>0.448552280664444</v>
+        <v>0.734304666519165</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.670119524002075</v>
+        <v>-3.189141035079956</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.548384547233582</v>
+        <v>10.00070762634277</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Up Mariana.m4a</t>
+          <t>Up3 Joel.wav</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1850,53 +1850,53 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-316.7931518554688</v>
+        <v>88.25578308105469</v>
       </c>
       <c r="B26" t="n">
-        <v>159.8381195068359</v>
+        <v>57.50599670410156</v>
       </c>
       <c r="C26" t="n">
-        <v>9.667288780212402</v>
+        <v>-9.737007141113281</v>
       </c>
       <c r="D26" t="n">
-        <v>27.56973266601562</v>
+        <v>5.279827117919922</v>
       </c>
       <c r="E26" t="n">
-        <v>-19.59236335754395</v>
+        <v>-7.31373405456543</v>
       </c>
       <c r="F26" t="n">
-        <v>23.98847198486328</v>
+        <v>-5.414810657501221</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3396598398685455</v>
+        <v>18.22062683105469</v>
       </c>
       <c r="H26" t="n">
-        <v>17.4832706451416</v>
+        <v>-14.10189723968506</v>
       </c>
       <c r="I26" t="n">
-        <v>19.35831642150879</v>
+        <v>0.4736920595169067</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.05820178985596</v>
+        <v>3.454010725021362</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.33665943145752</v>
+        <v>3.362349033355713</v>
       </c>
       <c r="L26" t="n">
-        <v>6.004086017608643</v>
+        <v>1.270719051361084</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.976099491119385</v>
+        <v>-8.611547470092773</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Up1 Mariana.m4a</t>
+          <t>Up4 Joel.wav</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -1906,53 +1906,53 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-289.3328247070312</v>
+        <v>69.98244476318359</v>
       </c>
       <c r="B27" t="n">
-        <v>152.9920959472656</v>
+        <v>68.96781921386719</v>
       </c>
       <c r="C27" t="n">
-        <v>-10.9343957901001</v>
+        <v>-11.50281810760498</v>
       </c>
       <c r="D27" t="n">
-        <v>32.75740051269531</v>
+        <v>14.05529022216797</v>
       </c>
       <c r="E27" t="n">
-        <v>-40.65970230102539</v>
+        <v>-7.916312217712402</v>
       </c>
       <c r="F27" t="n">
-        <v>18.88009452819824</v>
+        <v>-0.6288943290710449</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.408785104751587</v>
+        <v>15.61032676696777</v>
       </c>
       <c r="H27" t="n">
-        <v>19.97648429870605</v>
+        <v>-8.027802467346191</v>
       </c>
       <c r="I27" t="n">
-        <v>9.217135429382324</v>
+        <v>-1.528444409370422</v>
       </c>
       <c r="J27" t="n">
-        <v>-20.47669792175293</v>
+        <v>8.973652839660645</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7593949437141418</v>
+        <v>0.5921351313591003</v>
       </c>
       <c r="L27" t="n">
-        <v>11.04682445526123</v>
+        <v>3.59762716293335</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.623789310455322</v>
+        <v>-2.190004348754883</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Up10 Mariana.m4a</t>
+          <t>Up5 Joel.wav</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -1962,53 +1962,53 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-300.7842407226562</v>
+        <v>74.13119506835938</v>
       </c>
       <c r="B28" t="n">
-        <v>164.4346160888672</v>
+        <v>64.00780487060547</v>
       </c>
       <c r="C28" t="n">
-        <v>10.26668167114258</v>
+        <v>-17.73674583435059</v>
       </c>
       <c r="D28" t="n">
-        <v>14.31931400299072</v>
+        <v>17.59664535522461</v>
       </c>
       <c r="E28" t="n">
-        <v>-33.67021179199219</v>
+        <v>-10.39289283752441</v>
       </c>
       <c r="F28" t="n">
-        <v>11.15367126464844</v>
+        <v>3.011325359344482</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.299031972885132</v>
+        <v>7.9043869972229</v>
       </c>
       <c r="H28" t="n">
-        <v>11.55697631835938</v>
+        <v>-5.559561729431152</v>
       </c>
       <c r="I28" t="n">
-        <v>6.186204433441162</v>
+        <v>0.2081146240234375</v>
       </c>
       <c r="J28" t="n">
-        <v>-18.30887413024902</v>
+        <v>5.572865962982178</v>
       </c>
       <c r="K28" t="n">
-        <v>4.843581676483154</v>
+        <v>0.7636615633964539</v>
       </c>
       <c r="L28" t="n">
-        <v>14.22311878204346</v>
+        <v>6.170965671539307</v>
       </c>
       <c r="M28" t="n">
-        <v>-5.581329345703125</v>
+        <v>-4.252102375030518</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Up11 Mariana.m4a</t>
+          <t>Up6 Joel.wav</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2018,53 +2018,53 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-303.9783630371094</v>
+        <v>-51.1192626953125</v>
       </c>
       <c r="B29" t="n">
-        <v>164.4464111328125</v>
+        <v>117.3904418945312</v>
       </c>
       <c r="C29" t="n">
-        <v>-9.132596969604492</v>
+        <v>-30.40019226074219</v>
       </c>
       <c r="D29" t="n">
-        <v>22.12022399902344</v>
+        <v>22.74531173706055</v>
       </c>
       <c r="E29" t="n">
-        <v>-14.24733257293701</v>
+        <v>-14.70256805419922</v>
       </c>
       <c r="F29" t="n">
-        <v>17.00473213195801</v>
+        <v>-6.621948719024658</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.870904207229614</v>
+        <v>10.52336311340332</v>
       </c>
       <c r="H29" t="n">
-        <v>12.61378765106201</v>
+        <v>-17.26933670043945</v>
       </c>
       <c r="I29" t="n">
-        <v>31.5009822845459</v>
+        <v>15.78891468048096</v>
       </c>
       <c r="J29" t="n">
-        <v>-24.34177207946777</v>
+        <v>7.230295181274414</v>
       </c>
       <c r="K29" t="n">
-        <v>-18.7939567565918</v>
+        <v>4.03924036026001</v>
       </c>
       <c r="L29" t="n">
-        <v>15.50065326690674</v>
+        <v>-2.767011642456055</v>
       </c>
       <c r="M29" t="n">
-        <v>-10.18114471435547</v>
+        <v>2.412254333496094</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Up2 Mariana.m4a</t>
+          <t>Up7 Joel.wav</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2074,53 +2074,53 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-333.2005310058594</v>
+        <v>86.50965881347656</v>
       </c>
       <c r="B30" t="n">
-        <v>156.244873046875</v>
+        <v>62.87178421020508</v>
       </c>
       <c r="C30" t="n">
-        <v>-3.129465103149414</v>
+        <v>-12.98698329925537</v>
       </c>
       <c r="D30" t="n">
-        <v>26.5577449798584</v>
+        <v>14.75119495391846</v>
       </c>
       <c r="E30" t="n">
-        <v>-18.57096862792969</v>
+        <v>-14.73324298858643</v>
       </c>
       <c r="F30" t="n">
-        <v>21.73746490478516</v>
+        <v>-0.8880600929260254</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3010541498661041</v>
+        <v>9.016440391540527</v>
       </c>
       <c r="H30" t="n">
-        <v>14.58752822875977</v>
+        <v>-12.23507881164551</v>
       </c>
       <c r="I30" t="n">
-        <v>19.11462211608887</v>
+        <v>1.289515614509583</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.54855918884277</v>
+        <v>3.271676063537598</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.491666316986084</v>
+        <v>-1.424529194831848</v>
       </c>
       <c r="L30" t="n">
-        <v>6.726057529449463</v>
+        <v>0.5591740608215332</v>
       </c>
       <c r="M30" t="n">
-        <v>-5.087238788604736</v>
+        <v>-2.191425323486328</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Up3 Mariana.m4a</t>
+          <t>Up8 Joel.wav</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2130,53 +2130,53 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-325.018310546875</v>
+        <v>-23.06859970092773</v>
       </c>
       <c r="B31" t="n">
-        <v>176.98974609375</v>
+        <v>137.9472045898438</v>
       </c>
       <c r="C31" t="n">
-        <v>-11.86777877807617</v>
+        <v>-26.18479156494141</v>
       </c>
       <c r="D31" t="n">
-        <v>18.72822380065918</v>
+        <v>22.01977157592773</v>
       </c>
       <c r="E31" t="n">
-        <v>-23.36372375488281</v>
+        <v>-18.64120483398438</v>
       </c>
       <c r="F31" t="n">
-        <v>26.12260437011719</v>
+        <v>2.045474052429199</v>
       </c>
       <c r="G31" t="n">
-        <v>-3.701066732406616</v>
+        <v>13.34281158447266</v>
       </c>
       <c r="H31" t="n">
-        <v>16.15407371520996</v>
+        <v>-9.355486869812012</v>
       </c>
       <c r="I31" t="n">
-        <v>16.56460571289062</v>
+        <v>5.80120849609375</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.60554313659668</v>
+        <v>3.232617855072021</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.200514316558838</v>
+        <v>-0.3744091391563416</v>
       </c>
       <c r="L31" t="n">
-        <v>2.23934531211853</v>
+        <v>3.470405340194702</v>
       </c>
       <c r="M31" t="n">
-        <v>-5.097475051879883</v>
+        <v>1.964379668235779</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Up4 Mariana.m4a</t>
+          <t>Up9 Joel.wav</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2186,333 +2186,333 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-267.8022766113281</v>
+        <v>-38.81666946411133</v>
       </c>
       <c r="B32" t="n">
-        <v>162.8642120361328</v>
+        <v>144.4555358886719</v>
       </c>
       <c r="C32" t="n">
-        <v>7.828232288360596</v>
+        <v>-36.67446899414062</v>
       </c>
       <c r="D32" t="n">
-        <v>16.25493049621582</v>
+        <v>37.58754730224609</v>
       </c>
       <c r="E32" t="n">
-        <v>-38.71776962280273</v>
+        <v>-2.609708309173584</v>
       </c>
       <c r="F32" t="n">
-        <v>9.67104434967041</v>
+        <v>-21.82903671264648</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.150895476341248</v>
+        <v>0.3819043636322021</v>
       </c>
       <c r="H32" t="n">
-        <v>18.26862907409668</v>
+        <v>-10.09470748901367</v>
       </c>
       <c r="I32" t="n">
-        <v>14.02985286712646</v>
+        <v>9.164710998535156</v>
       </c>
       <c r="J32" t="n">
-        <v>-22.69136238098145</v>
+        <v>9.678985595703125</v>
       </c>
       <c r="K32" t="n">
-        <v>0.695077121257782</v>
+        <v>-10.30873966217041</v>
       </c>
       <c r="L32" t="n">
-        <v>11.38204669952393</v>
+        <v>-6.561491966247559</v>
       </c>
       <c r="M32" t="n">
-        <v>-14.3076810836792</v>
+        <v>-3.246865749359131</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Up5 Mariana.m4a</t>
+          <t>Down Joel.wav</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-299.4425964355469</v>
+        <v>-59.96945571899414</v>
       </c>
       <c r="B33" t="n">
-        <v>155.9931640625</v>
+        <v>149.7138671875</v>
       </c>
       <c r="C33" t="n">
-        <v>3.272412061691284</v>
+        <v>-27.4206714630127</v>
       </c>
       <c r="D33" t="n">
-        <v>18.16885185241699</v>
+        <v>27.07188606262207</v>
       </c>
       <c r="E33" t="n">
-        <v>-29.34106636047363</v>
+        <v>12.03425979614258</v>
       </c>
       <c r="F33" t="n">
-        <v>11.57119464874268</v>
+        <v>-22.39077377319336</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.672499299049377</v>
+        <v>1.191161394119263</v>
       </c>
       <c r="H33" t="n">
-        <v>20.56723403930664</v>
+        <v>-8.85800838470459</v>
       </c>
       <c r="I33" t="n">
-        <v>8.781693458557129</v>
+        <v>13.44608688354492</v>
       </c>
       <c r="J33" t="n">
-        <v>-21.43767738342285</v>
+        <v>-0.1116341352462769</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.2720103561878204</v>
+        <v>-11.43355369567871</v>
       </c>
       <c r="L33" t="n">
-        <v>4.74152135848999</v>
+        <v>-4.635310649871826</v>
       </c>
       <c r="M33" t="n">
-        <v>-10.57860565185547</v>
+        <v>-8.691716194152832</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Up6 Mariana.m4a</t>
+          <t>Down1 Joel.wav</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-332.5428161621094</v>
+        <v>-10.28546333312988</v>
       </c>
       <c r="B34" t="n">
-        <v>137.2420501708984</v>
+        <v>141.5125122070312</v>
       </c>
       <c r="C34" t="n">
-        <v>3.469392776489258</v>
+        <v>-31.33033752441406</v>
       </c>
       <c r="D34" t="n">
-        <v>23.0447826385498</v>
+        <v>29.23284339904785</v>
       </c>
       <c r="E34" t="n">
-        <v>-17.42586898803711</v>
+        <v>-3.658007621765137</v>
       </c>
       <c r="F34" t="n">
-        <v>17.96489524841309</v>
+        <v>-21.56808662414551</v>
       </c>
       <c r="G34" t="n">
-        <v>2.755120515823364</v>
+        <v>2.317570209503174</v>
       </c>
       <c r="H34" t="n">
-        <v>15.66798877716064</v>
+        <v>-17.94597434997559</v>
       </c>
       <c r="I34" t="n">
-        <v>7.469368457794189</v>
+        <v>21.48738479614258</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.41288471221924</v>
+        <v>1.767487049102783</v>
       </c>
       <c r="K34" t="n">
-        <v>1.257885217666626</v>
+        <v>-19.3849048614502</v>
       </c>
       <c r="L34" t="n">
-        <v>7.031112670898438</v>
+        <v>0.7288873195648193</v>
       </c>
       <c r="M34" t="n">
-        <v>-7.250665664672852</v>
+        <v>-1.387025356292725</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Up7 Mariana.m4a</t>
+          <t>Down2 Joel.wav</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-328.9590759277344</v>
+        <v>-65.70687866210938</v>
       </c>
       <c r="B35" t="n">
-        <v>150.4453125</v>
+        <v>153.6451568603516</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.955182433128357</v>
+        <v>-18.49061965942383</v>
       </c>
       <c r="D35" t="n">
-        <v>23.19268226623535</v>
+        <v>30.66348266601562</v>
       </c>
       <c r="E35" t="n">
-        <v>-30.0288028717041</v>
+        <v>1.563776612281799</v>
       </c>
       <c r="F35" t="n">
-        <v>11.2949333190918</v>
+        <v>-10.99791145324707</v>
       </c>
       <c r="G35" t="n">
-        <v>5.338920116424561</v>
+        <v>-5.358700752258301</v>
       </c>
       <c r="H35" t="n">
-        <v>17.46496772766113</v>
+        <v>-7.456603527069092</v>
       </c>
       <c r="I35" t="n">
-        <v>7.222009658813477</v>
+        <v>16.07112884521484</v>
       </c>
       <c r="J35" t="n">
-        <v>-17.34977912902832</v>
+        <v>2.323585748672485</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.08716672658920288</v>
+        <v>-6.439966678619385</v>
       </c>
       <c r="L35" t="n">
-        <v>10.12353801727295</v>
+        <v>-5.729353427886963</v>
       </c>
       <c r="M35" t="n">
-        <v>-8.343072891235352</v>
+        <v>1.216680526733398</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Up8 Mariana.m4a</t>
+          <t>Down3 Joel.wav</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-308.0969543457031</v>
+        <v>-32.6185417175293</v>
       </c>
       <c r="B36" t="n">
-        <v>148.83056640625</v>
+        <v>122.7339324951172</v>
       </c>
       <c r="C36" t="n">
-        <v>2.057168960571289</v>
+        <v>-29.69515037536621</v>
       </c>
       <c r="D36" t="n">
-        <v>29.86710548400879</v>
+        <v>32.22972106933594</v>
       </c>
       <c r="E36" t="n">
-        <v>-32.61809158325195</v>
+        <v>-9.453845024108887</v>
       </c>
       <c r="F36" t="n">
-        <v>13.00045776367188</v>
+        <v>-5.141208648681641</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.541706085205078</v>
+        <v>-4.584595680236816</v>
       </c>
       <c r="H36" t="n">
-        <v>18.90066528320312</v>
+        <v>-21.86382293701172</v>
       </c>
       <c r="I36" t="n">
-        <v>9.89659595489502</v>
+        <v>10.29101181030273</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.63266563415527</v>
+        <v>3.251049041748047</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.3330811560153961</v>
+        <v>-14.27432060241699</v>
       </c>
       <c r="L36" t="n">
-        <v>9.45768928527832</v>
+        <v>0.1205525398254395</v>
       </c>
       <c r="M36" t="n">
-        <v>-10.61479187011719</v>
+        <v>-8.163700103759766</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Up9 Mariana.m4a</t>
+          <t>Down4 Joel.wav</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-169.7220306396484</v>
+        <v>-4.316352844238281</v>
       </c>
       <c r="B37" t="n">
-        <v>164.0709838867188</v>
+        <v>87.53806304931641</v>
       </c>
       <c r="C37" t="n">
-        <v>13.79395771026611</v>
+        <v>-1.913559317588806</v>
       </c>
       <c r="D37" t="n">
-        <v>14.66062641143799</v>
+        <v>3.133590459823608</v>
       </c>
       <c r="E37" t="n">
-        <v>-20.03698921203613</v>
+        <v>3.318132400512695</v>
       </c>
       <c r="F37" t="n">
-        <v>7.814794063568115</v>
+        <v>-8.436339378356934</v>
       </c>
       <c r="G37" t="n">
-        <v>-5.577279567718506</v>
+        <v>-8.08600902557373</v>
       </c>
       <c r="H37" t="n">
-        <v>25.46661376953125</v>
+        <v>-3.350376844406128</v>
       </c>
       <c r="I37" t="n">
-        <v>-23.73595237731934</v>
+        <v>9.026849746704102</v>
       </c>
       <c r="J37" t="n">
-        <v>-12.04768657684326</v>
+        <v>4.134526252746582</v>
       </c>
       <c r="K37" t="n">
-        <v>13.60510540008545</v>
+        <v>-8.483448028564453</v>
       </c>
       <c r="L37" t="n">
-        <v>-5.728031158447266</v>
+        <v>-5.845293045043945</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5453471541404724</v>
+        <v>-1.310791969299316</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Down Mariana.m4a</t>
+          <t>Down5 Joel.wav</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2522,53 +2522,53 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-179.7423553466797</v>
+        <v>-43.68737411499023</v>
       </c>
       <c r="B38" t="n">
-        <v>146.3544616699219</v>
+        <v>134.5790557861328</v>
       </c>
       <c r="C38" t="n">
-        <v>-11.42390441894531</v>
+        <v>-25.65071678161621</v>
       </c>
       <c r="D38" t="n">
-        <v>30.79145622253418</v>
+        <v>29.69024658203125</v>
       </c>
       <c r="E38" t="n">
-        <v>-31.79669952392578</v>
+        <v>-0.8249391317367554</v>
       </c>
       <c r="F38" t="n">
-        <v>26.56219673156738</v>
+        <v>-12.54806995391846</v>
       </c>
       <c r="G38" t="n">
-        <v>-6.878900051116943</v>
+        <v>10.16463661193848</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.020455718040466</v>
+        <v>-7.455234527587891</v>
       </c>
       <c r="I38" t="n">
-        <v>-9.413234710693359</v>
+        <v>6.80546760559082</v>
       </c>
       <c r="J38" t="n">
-        <v>-17.26572418212891</v>
+        <v>2.297531843185425</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.347594738006592</v>
+        <v>-3.865301370620728</v>
       </c>
       <c r="L38" t="n">
-        <v>10.87221813201904</v>
+        <v>-1.468611717224121</v>
       </c>
       <c r="M38" t="n">
-        <v>-15.83783435821533</v>
+        <v>-4.237308979034424</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Down1 Mariana.m4a</t>
+          <t>Down6 Joel.wav</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2578,53 +2578,53 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-222.4703826904297</v>
+        <v>-11.40614318847656</v>
       </c>
       <c r="B39" t="n">
-        <v>165.5427703857422</v>
+        <v>148.4408264160156</v>
       </c>
       <c r="C39" t="n">
-        <v>-9.080623626708984</v>
+        <v>-39.38896179199219</v>
       </c>
       <c r="D39" t="n">
-        <v>34.40157318115234</v>
+        <v>25.33176422119141</v>
       </c>
       <c r="E39" t="n">
-        <v>-40.28592300415039</v>
+        <v>-13.31790351867676</v>
       </c>
       <c r="F39" t="n">
-        <v>21.67230224609375</v>
+        <v>-15.88465881347656</v>
       </c>
       <c r="G39" t="n">
-        <v>-4.150908946990967</v>
+        <v>8.46068000793457</v>
       </c>
       <c r="H39" t="n">
-        <v>-5.405185699462891</v>
+        <v>-10.27483940124512</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9796097874641418</v>
+        <v>9.024722099304199</v>
       </c>
       <c r="J39" t="n">
-        <v>-18.53535270690918</v>
+        <v>-2.581375122070312</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.071200847625732</v>
+        <v>-8.85817813873291</v>
       </c>
       <c r="L39" t="n">
-        <v>5.272520542144775</v>
+        <v>-6.436631202697754</v>
       </c>
       <c r="M39" t="n">
-        <v>-13.83665752410889</v>
+        <v>-8.631892204284668</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Down10 Mariana.m4a</t>
+          <t>Down7 Joel.wav</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2634,53 +2634,53 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-223.8843231201172</v>
+        <v>-83.86772155761719</v>
       </c>
       <c r="B40" t="n">
-        <v>187.7896270751953</v>
+        <v>142.6986541748047</v>
       </c>
       <c r="C40" t="n">
-        <v>-10.66405200958252</v>
+        <v>-33.02392196655273</v>
       </c>
       <c r="D40" t="n">
-        <v>25.03379058837891</v>
+        <v>31.7792911529541</v>
       </c>
       <c r="E40" t="n">
-        <v>-31.42597007751465</v>
+        <v>-16.46760940551758</v>
       </c>
       <c r="F40" t="n">
-        <v>29.08467102050781</v>
+        <v>-4.379992008209229</v>
       </c>
       <c r="G40" t="n">
-        <v>-3.615395784378052</v>
+        <v>10.87947082519531</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.406959295272827</v>
+        <v>-16.77433013916016</v>
       </c>
       <c r="I40" t="n">
-        <v>3.775293111801147</v>
+        <v>16.44384002685547</v>
       </c>
       <c r="J40" t="n">
-        <v>-21.8518009185791</v>
+        <v>5.333250522613525</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.3777779042720795</v>
+        <v>-7.747468948364258</v>
       </c>
       <c r="L40" t="n">
-        <v>3.656583547592163</v>
+        <v>-3.792082786560059</v>
       </c>
       <c r="M40" t="n">
-        <v>-17.8358039855957</v>
+        <v>-6.986350536346436</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Down11 Mariana.m4a</t>
+          <t>Down8 Joel.wav</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -2690,53 +2690,53 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-180.6804656982422</v>
+        <v>-56.05964660644531</v>
       </c>
       <c r="B41" t="n">
-        <v>150.7134246826172</v>
+        <v>134.0142517089844</v>
       </c>
       <c r="C41" t="n">
-        <v>-14.48606109619141</v>
+        <v>-38.56221008300781</v>
       </c>
       <c r="D41" t="n">
-        <v>29.88214111328125</v>
+        <v>23.0645751953125</v>
       </c>
       <c r="E41" t="n">
-        <v>-43.18258285522461</v>
+        <v>-7.451848983764648</v>
       </c>
       <c r="F41" t="n">
-        <v>33.08852005004883</v>
+        <v>-3.750684261322021</v>
       </c>
       <c r="G41" t="n">
-        <v>-9.28621768951416</v>
+        <v>9.574556350708008</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.283596754074097</v>
+        <v>-19.94680786132812</v>
       </c>
       <c r="I41" t="n">
-        <v>-11.49045848846436</v>
+        <v>3.624521970748901</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.09026908874512</v>
+        <v>4.395712375640869</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.581276416778564</v>
+        <v>-5.062682151794434</v>
       </c>
       <c r="L41" t="n">
-        <v>8.209700584411621</v>
+        <v>-5.979804515838623</v>
       </c>
       <c r="M41" t="n">
-        <v>-13.08615970611572</v>
+        <v>-5.002154350280762</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Down2 Mariana.m4a</t>
+          <t>Down9 Joel.wav</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -2746,399 +2746,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>-175.8802337646484</v>
-      </c>
-      <c r="B42" t="n">
-        <v>163.1787261962891</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-30.16866874694824</v>
-      </c>
-      <c r="D42" t="n">
-        <v>33.21114730834961</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-42.98654556274414</v>
-      </c>
-      <c r="F42" t="n">
-        <v>26.70092582702637</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-14.23777484893799</v>
-      </c>
-      <c r="H42" t="n">
-        <v>4.343015670776367</v>
-      </c>
-      <c r="I42" t="n">
-        <v>-14.85474681854248</v>
-      </c>
-      <c r="J42" t="n">
-        <v>-24.19658088684082</v>
-      </c>
-      <c r="K42" t="n">
-        <v>-1.746057033538818</v>
-      </c>
-      <c r="L42" t="n">
-        <v>8.359879493713379</v>
-      </c>
-      <c r="M42" t="n">
-        <v>-20.13007354736328</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Down3 Mariana.m4a</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>-195.1746368408203</v>
-      </c>
-      <c r="B43" t="n">
-        <v>159.0303192138672</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-18.27469825744629</v>
-      </c>
-      <c r="D43" t="n">
-        <v>26.60164642333984</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-50.52536010742188</v>
-      </c>
-      <c r="F43" t="n">
-        <v>30.73587036132812</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-9.303877830505371</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-0.4836514890193939</v>
-      </c>
-      <c r="I43" t="n">
-        <v>-8.370524406433105</v>
-      </c>
-      <c r="J43" t="n">
-        <v>-16.19344520568848</v>
-      </c>
-      <c r="K43" t="n">
-        <v>-8.349696159362793</v>
-      </c>
-      <c r="L43" t="n">
-        <v>11.43166828155518</v>
-      </c>
-      <c r="M43" t="n">
-        <v>-16.9129581451416</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Down4 Mariana.m4a</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>-202.5100555419922</v>
-      </c>
-      <c r="B44" t="n">
-        <v>162.5060882568359</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-12.82490825653076</v>
-      </c>
-      <c r="D44" t="n">
-        <v>36.74423980712891</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-36.37984466552734</v>
-      </c>
-      <c r="F44" t="n">
-        <v>22.57111358642578</v>
-      </c>
-      <c r="G44" t="n">
-        <v>-8.472342491149902</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-3.26734447479248</v>
-      </c>
-      <c r="I44" t="n">
-        <v>-2.973716735839844</v>
-      </c>
-      <c r="J44" t="n">
-        <v>-24.13687705993652</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-5.516200542449951</v>
-      </c>
-      <c r="L44" t="n">
-        <v>5.432977676391602</v>
-      </c>
-      <c r="M44" t="n">
-        <v>-12.31193542480469</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Down5 Mariana.m4a</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>-196.591064453125</v>
-      </c>
-      <c r="B45" t="n">
-        <v>164.3428497314453</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-15.54982662200928</v>
-      </c>
-      <c r="D45" t="n">
-        <v>27.70147514343262</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-42.7592658996582</v>
-      </c>
-      <c r="F45" t="n">
-        <v>23.48557472229004</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-7.670164108276367</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.1672782897949219</v>
-      </c>
-      <c r="I45" t="n">
-        <v>-10.72808170318604</v>
-      </c>
-      <c r="J45" t="n">
-        <v>-22.22047424316406</v>
-      </c>
-      <c r="K45" t="n">
-        <v>-3.347694635391235</v>
-      </c>
-      <c r="L45" t="n">
-        <v>8.128780364990234</v>
-      </c>
-      <c r="M45" t="n">
-        <v>-15.06269073486328</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Down6 Mariana.m4a</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>-203.0472564697266</v>
-      </c>
-      <c r="B46" t="n">
-        <v>164.7646636962891</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-14.09083271026611</v>
-      </c>
-      <c r="D46" t="n">
-        <v>33.46609115600586</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-32.95969390869141</v>
-      </c>
-      <c r="F46" t="n">
-        <v>24.65498924255371</v>
-      </c>
-      <c r="G46" t="n">
-        <v>-6.622889041900635</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-2.515846729278564</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-6.971050262451172</v>
-      </c>
-      <c r="J46" t="n">
-        <v>-20.06133842468262</v>
-      </c>
-      <c r="K46" t="n">
-        <v>-0.3501172065734863</v>
-      </c>
-      <c r="L46" t="n">
-        <v>9.528847694396973</v>
-      </c>
-      <c r="M46" t="n">
-        <v>-14.67333984375</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Down7 Mariana.m4a</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>-216.9405059814453</v>
-      </c>
-      <c r="B47" t="n">
-        <v>146.1065063476562</v>
-      </c>
-      <c r="C47" t="n">
-        <v>4.8263840675354</v>
-      </c>
-      <c r="D47" t="n">
-        <v>37.83620834350586</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-40.00489044189453</v>
-      </c>
-      <c r="F47" t="n">
-        <v>31.58793449401855</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-7.556925296783447</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-4.947163105010986</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-6.464698791503906</v>
-      </c>
-      <c r="J47" t="n">
-        <v>-9.107434272766113</v>
-      </c>
-      <c r="K47" t="n">
-        <v>-4.027056217193604</v>
-      </c>
-      <c r="L47" t="n">
-        <v>8.442744255065918</v>
-      </c>
-      <c r="M47" t="n">
-        <v>-21.50909423828125</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Down8 Mariana.m4a</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>-206.2462615966797</v>
-      </c>
-      <c r="B48" t="n">
-        <v>147.8334350585938</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-2.481975793838501</v>
-      </c>
-      <c r="D48" t="n">
-        <v>36.63810348510742</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-43.74824142456055</v>
-      </c>
-      <c r="F48" t="n">
-        <v>28.13072776794434</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-7.846312046051025</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-2.593235731124878</v>
-      </c>
-      <c r="I48" t="n">
-        <v>-12.28597736358643</v>
-      </c>
-      <c r="J48" t="n">
-        <v>-11.31254863739014</v>
-      </c>
-      <c r="K48" t="n">
-        <v>-4.820269107818604</v>
-      </c>
-      <c r="L48" t="n">
-        <v>7.493367671966553</v>
-      </c>
-      <c r="M48" t="n">
-        <v>-18.94203186035156</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Down9 Mariana.m4a</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Mariana</t>
+          <t>Joel</t>
         </is>
       </c>
     </row>

--- a/mfcc_features_avg.xlsx
+++ b/mfcc_features_avg.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,43 +512,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-71.8040771484375</v>
+        <v>-154.4829254150391</v>
       </c>
       <c r="B2" t="n">
-        <v>112.2355728149414</v>
+        <v>114.2450942993164</v>
       </c>
       <c r="C2" t="n">
-        <v>-15.18389797210693</v>
+        <v>-17.18775939941406</v>
       </c>
       <c r="D2" t="n">
-        <v>23.55993270874023</v>
+        <v>27.92997741699219</v>
       </c>
       <c r="E2" t="n">
-        <v>6.407943248748779</v>
+        <v>3.474710941314697</v>
       </c>
       <c r="F2" t="n">
-        <v>-20.31331253051758</v>
+        <v>-18.5345573425293</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.966050028800964</v>
+        <v>-0.4410750269889832</v>
       </c>
       <c r="H2" t="n">
-        <v>-13.93924522399902</v>
+        <v>-14.91102600097656</v>
       </c>
       <c r="I2" t="n">
-        <v>14.22094058990479</v>
+        <v>11.96564388275146</v>
       </c>
       <c r="J2" t="n">
-        <v>6.74221134185791</v>
+        <v>5.632670879364014</v>
       </c>
       <c r="K2" t="n">
-        <v>2.716077089309692</v>
+        <v>0.1480444222688675</v>
       </c>
       <c r="L2" t="n">
-        <v>-6.647804260253906</v>
+        <v>-7.012741088867188</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6647546291351318</v>
+        <v>-0.2684025466442108</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -568,43 +568,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-106.4817657470703</v>
+        <v>-180.4396057128906</v>
       </c>
       <c r="B3" t="n">
-        <v>128.2368621826172</v>
+        <v>129.8936462402344</v>
       </c>
       <c r="C3" t="n">
-        <v>-22.19016647338867</v>
+        <v>-22.14182090759277</v>
       </c>
       <c r="D3" t="n">
-        <v>18.16694068908691</v>
+        <v>17.6969165802002</v>
       </c>
       <c r="E3" t="n">
-        <v>3.970492124557495</v>
+        <v>1.908202409744263</v>
       </c>
       <c r="F3" t="n">
-        <v>-19.33951950073242</v>
+        <v>-15.0469331741333</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.238811016082764</v>
+        <v>-2.656670093536377</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.847513198852539</v>
+        <v>-5.819331169128418</v>
       </c>
       <c r="I3" t="n">
-        <v>10.98017120361328</v>
+        <v>9.836094856262207</v>
       </c>
       <c r="J3" t="n">
-        <v>6.029256820678711</v>
+        <v>5.316262245178223</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.01313424110412598</v>
+        <v>-0.510789692401886</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6434212923049927</v>
+        <v>-1.132724642753601</v>
       </c>
       <c r="M3" t="n">
-        <v>3.959981203079224</v>
+        <v>4.581978321075439</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -624,43 +624,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-103.7057723999023</v>
+        <v>-185.9740753173828</v>
       </c>
       <c r="B4" t="n">
-        <v>107.1809921264648</v>
+        <v>109.8975067138672</v>
       </c>
       <c r="C4" t="n">
-        <v>-4.075252056121826</v>
+        <v>-7.215966701507568</v>
       </c>
       <c r="D4" t="n">
-        <v>17.16353988647461</v>
+        <v>20.73722457885742</v>
       </c>
       <c r="E4" t="n">
-        <v>8.966035842895508</v>
+        <v>8.946657180786133</v>
       </c>
       <c r="F4" t="n">
-        <v>-15.49599266052246</v>
+        <v>-12.0593433380127</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.93409252166748</v>
+        <v>-3.228121995925903</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.3892822265625</v>
+        <v>-11.61141872406006</v>
       </c>
       <c r="I4" t="n">
-        <v>4.68236255645752</v>
+        <v>5.27098560333252</v>
       </c>
       <c r="J4" t="n">
-        <v>4.859355449676514</v>
+        <v>3.986615657806396</v>
       </c>
       <c r="K4" t="n">
-        <v>1.647185087203979</v>
+        <v>2.499234676361084</v>
       </c>
       <c r="L4" t="n">
-        <v>6.217882633209229</v>
+        <v>3.145023822784424</v>
       </c>
       <c r="M4" t="n">
-        <v>1.953668832778931</v>
+        <v>1.751867294311523</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,43 +680,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-76.4688720703125</v>
+        <v>-149.7996520996094</v>
       </c>
       <c r="B5" t="n">
-        <v>122.8817749023438</v>
+        <v>122.4405364990234</v>
       </c>
       <c r="C5" t="n">
-        <v>-18.81569671630859</v>
+        <v>-19.56806182861328</v>
       </c>
       <c r="D5" t="n">
-        <v>18.7939281463623</v>
+        <v>18.17929840087891</v>
       </c>
       <c r="E5" t="n">
-        <v>6.611835479736328</v>
+        <v>6.317056179046631</v>
       </c>
       <c r="F5" t="n">
-        <v>-17.07516098022461</v>
+        <v>-17.02126884460449</v>
       </c>
       <c r="G5" t="n">
-        <v>0.15595743060112</v>
+        <v>-0.370576947927475</v>
       </c>
       <c r="H5" t="n">
-        <v>-10.1917552947998</v>
+        <v>-11.36838340759277</v>
       </c>
       <c r="I5" t="n">
-        <v>1.33712100982666</v>
+        <v>1.897351503372192</v>
       </c>
       <c r="J5" t="n">
-        <v>1.215933561325073</v>
+        <v>0.07841406017541885</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4178054332733154</v>
+        <v>-1.556527137756348</v>
       </c>
       <c r="L5" t="n">
-        <v>3.551511287689209</v>
+        <v>2.128699779510498</v>
       </c>
       <c r="M5" t="n">
-        <v>3.748766899108887</v>
+        <v>4.548010349273682</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -736,43 +736,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-91.39448547363281</v>
+        <v>-161.3145446777344</v>
       </c>
       <c r="B6" t="n">
-        <v>117.1110687255859</v>
+        <v>113.2850189208984</v>
       </c>
       <c r="C6" t="n">
-        <v>-14.32407474517822</v>
+        <v>-17.59431076049805</v>
       </c>
       <c r="D6" t="n">
-        <v>19.93028831481934</v>
+        <v>19.37857246398926</v>
       </c>
       <c r="E6" t="n">
-        <v>9.125797271728516</v>
+        <v>6.439919948577881</v>
       </c>
       <c r="F6" t="n">
-        <v>-23.57026863098145</v>
+        <v>-23.65594291687012</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.121702909469604</v>
+        <v>-0.743989109992981</v>
       </c>
       <c r="H6" t="n">
-        <v>-11.53048324584961</v>
+        <v>-13.69779682159424</v>
       </c>
       <c r="I6" t="n">
-        <v>13.14991664886475</v>
+        <v>12.72946834564209</v>
       </c>
       <c r="J6" t="n">
-        <v>7.004104614257812</v>
+        <v>6.229372501373291</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.109302520751953</v>
+        <v>-4.293410301208496</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.072667360305786</v>
+        <v>-3.566083908081055</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9757453203201294</v>
+        <v>0.9464184045791626</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -792,43 +792,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-71.15321350097656</v>
+        <v>-150.0155487060547</v>
       </c>
       <c r="B7" t="n">
-        <v>113.1995849609375</v>
+        <v>107.7287979125977</v>
       </c>
       <c r="C7" t="n">
-        <v>-20.76276206970215</v>
+        <v>-21.69366264343262</v>
       </c>
       <c r="D7" t="n">
-        <v>23.36148071289062</v>
+        <v>26.63031005859375</v>
       </c>
       <c r="E7" t="n">
-        <v>1.79542350769043</v>
+        <v>-0.2751089036464691</v>
       </c>
       <c r="F7" t="n">
-        <v>-19.34828758239746</v>
+        <v>-15.30207538604736</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5174171328544617</v>
+        <v>0.131047323346138</v>
       </c>
       <c r="H7" t="n">
-        <v>-12.81495571136475</v>
+        <v>-17.42232894897461</v>
       </c>
       <c r="I7" t="n">
-        <v>12.90143775939941</v>
+        <v>11.58583831787109</v>
       </c>
       <c r="J7" t="n">
-        <v>5.956028938293457</v>
+        <v>5.693809509277344</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.634991407394409</v>
+        <v>-4.771003723144531</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6303516626358032</v>
+        <v>0.1088680773973465</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2651865482330322</v>
+        <v>-0.8370293378829956</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -848,43 +848,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-99.24075317382812</v>
+        <v>-167.1927795410156</v>
       </c>
       <c r="B8" t="n">
-        <v>109.6936950683594</v>
+        <v>109.7833099365234</v>
       </c>
       <c r="C8" t="n">
-        <v>-12.60856056213379</v>
+        <v>-15.29550933837891</v>
       </c>
       <c r="D8" t="n">
-        <v>20.93209075927734</v>
+        <v>21.06215286254883</v>
       </c>
       <c r="E8" t="n">
-        <v>2.566448211669922</v>
+        <v>1.578771471977234</v>
       </c>
       <c r="F8" t="n">
-        <v>-15.27226829528809</v>
+        <v>-18.47139549255371</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6308063864707947</v>
+        <v>-2.160032987594604</v>
       </c>
       <c r="H8" t="n">
-        <v>-9.565656661987305</v>
+        <v>-12.34976100921631</v>
       </c>
       <c r="I8" t="n">
-        <v>12.68030166625977</v>
+        <v>12.6030445098877</v>
       </c>
       <c r="J8" t="n">
-        <v>4.734650135040283</v>
+        <v>5.206488132476807</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.260698318481445</v>
+        <v>-3.295578718185425</v>
       </c>
       <c r="L8" t="n">
-        <v>3.905904769897461</v>
+        <v>2.418928623199463</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.410958290100098</v>
+        <v>-0.8954119682312012</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -904,43 +904,43 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-21.45622253417969</v>
+        <v>-112.816162109375</v>
       </c>
       <c r="B9" t="n">
-        <v>89.19442749023438</v>
+        <v>98.16275024414062</v>
       </c>
       <c r="C9" t="n">
-        <v>-34.8651008605957</v>
+        <v>-37.32527542114258</v>
       </c>
       <c r="D9" t="n">
-        <v>17.43874168395996</v>
+        <v>14.76787376403809</v>
       </c>
       <c r="E9" t="n">
-        <v>6.898602485656738</v>
+        <v>9.431478500366211</v>
       </c>
       <c r="F9" t="n">
-        <v>-16.25429344177246</v>
+        <v>-12.16197395324707</v>
       </c>
       <c r="G9" t="n">
-        <v>10.77474594116211</v>
+        <v>4.728366374969482</v>
       </c>
       <c r="H9" t="n">
-        <v>-28.14611053466797</v>
+        <v>-26.13212013244629</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.318309307098389</v>
+        <v>-3.266095399856567</v>
       </c>
       <c r="J9" t="n">
-        <v>2.452599763870239</v>
+        <v>2.6382155418396</v>
       </c>
       <c r="K9" t="n">
-        <v>4.60897970199585</v>
+        <v>3.815670728683472</v>
       </c>
       <c r="L9" t="n">
-        <v>9.009366989135742</v>
+        <v>7.772402763366699</v>
       </c>
       <c r="M9" t="n">
-        <v>-9.263223648071289</v>
+        <v>-6.679268836975098</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -960,43 +960,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-85.11765289306641</v>
+        <v>-156.4335632324219</v>
       </c>
       <c r="B10" t="n">
-        <v>119.8439407348633</v>
+        <v>114.7543487548828</v>
       </c>
       <c r="C10" t="n">
-        <v>-23.95764923095703</v>
+        <v>-23.26803207397461</v>
       </c>
       <c r="D10" t="n">
-        <v>28.55070495605469</v>
+        <v>26.45456886291504</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7691645622253418</v>
+        <v>0.6788845062255859</v>
       </c>
       <c r="F10" t="n">
-        <v>-29.41290092468262</v>
+        <v>-25.84737586975098</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.710836410522461</v>
+        <v>0.6032291650772095</v>
       </c>
       <c r="H10" t="n">
-        <v>-14.48098850250244</v>
+        <v>-16.58570289611816</v>
       </c>
       <c r="I10" t="n">
-        <v>4.668339729309082</v>
+        <v>5.967980861663818</v>
       </c>
       <c r="J10" t="n">
-        <v>3.02626371383667</v>
+        <v>1.681537628173828</v>
       </c>
       <c r="K10" t="n">
-        <v>2.576141834259033</v>
+        <v>2.286431074142456</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2306655943393707</v>
+        <v>-0.7789088487625122</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5871131420135498</v>
+        <v>0.3708535730838776</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1016,43 +1016,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-40.19889068603516</v>
+        <v>-132.5841064453125</v>
       </c>
       <c r="B11" t="n">
-        <v>87.49761962890625</v>
+        <v>104.3727035522461</v>
       </c>
       <c r="C11" t="n">
-        <v>-22.050537109375</v>
+        <v>-24.25700378417969</v>
       </c>
       <c r="D11" t="n">
-        <v>28.09512710571289</v>
+        <v>22.45502662658691</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1879253387451172</v>
+        <v>7.178849220275879</v>
       </c>
       <c r="F11" t="n">
-        <v>-24.82884407043457</v>
+        <v>-23.75319671630859</v>
       </c>
       <c r="G11" t="n">
-        <v>9.162453651428223</v>
+        <v>2.63112211227417</v>
       </c>
       <c r="H11" t="n">
-        <v>-20.43125534057617</v>
+        <v>-18.88183403015137</v>
       </c>
       <c r="I11" t="n">
-        <v>6.291667461395264</v>
+        <v>6.473748683929443</v>
       </c>
       <c r="J11" t="n">
-        <v>4.021479606628418</v>
+        <v>5.664782524108887</v>
       </c>
       <c r="K11" t="n">
-        <v>5.579592704772949</v>
+        <v>-1.537061452865601</v>
       </c>
       <c r="L11" t="n">
-        <v>3.013643503189087</v>
+        <v>3.208592653274536</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.998010635375977</v>
+        <v>-5.324906349182129</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1072,43 +1072,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-36.17762756347656</v>
+        <v>-140.4809875488281</v>
       </c>
       <c r="B12" t="n">
-        <v>102.3365631103516</v>
+        <v>122.0556182861328</v>
       </c>
       <c r="C12" t="n">
-        <v>-32.84944152832031</v>
+        <v>-38.13889694213867</v>
       </c>
       <c r="D12" t="n">
-        <v>27.28002738952637</v>
+        <v>25.29310035705566</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.61792182922363</v>
+        <v>-11.39078712463379</v>
       </c>
       <c r="F12" t="n">
-        <v>-23.15808868408203</v>
+        <v>-19.42279434204102</v>
       </c>
       <c r="G12" t="n">
-        <v>6.84476375579834</v>
+        <v>0.6549185514450073</v>
       </c>
       <c r="H12" t="n">
-        <v>-20.80265808105469</v>
+        <v>-18.76600646972656</v>
       </c>
       <c r="I12" t="n">
-        <v>3.684324264526367</v>
+        <v>4.891191959381104</v>
       </c>
       <c r="J12" t="n">
-        <v>4.195711135864258</v>
+        <v>1.330928206443787</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.741775035858154</v>
+        <v>-1.761686086654663</v>
       </c>
       <c r="L12" t="n">
-        <v>6.893524169921875</v>
+        <v>4.575943946838379</v>
       </c>
       <c r="M12" t="n">
-        <v>-11.38441371917725</v>
+        <v>-9.800477981567383</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,43 +1128,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-80.72531890869141</v>
+        <v>-167.6164245605469</v>
       </c>
       <c r="B13" t="n">
-        <v>135.9575653076172</v>
+        <v>138.3794860839844</v>
       </c>
       <c r="C13" t="n">
-        <v>-39.11029052734375</v>
+        <v>-38.0563850402832</v>
       </c>
       <c r="D13" t="n">
-        <v>22.55585479736328</v>
+        <v>21.45431709289551</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.825613021850586</v>
+        <v>-5.586894989013672</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.34232234954834</v>
+        <v>-11.84983444213867</v>
       </c>
       <c r="G13" t="n">
-        <v>5.528236865997314</v>
+        <v>3.064724445343018</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.693671226501465</v>
+        <v>-10.51119232177734</v>
       </c>
       <c r="I13" t="n">
-        <v>3.221199512481689</v>
+        <v>4.479099273681641</v>
       </c>
       <c r="J13" t="n">
-        <v>5.380485534667969</v>
+        <v>5.610386371612549</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.094040632247925</v>
+        <v>-2.158938407897949</v>
       </c>
       <c r="L13" t="n">
-        <v>2.056243419647217</v>
+        <v>1.357713341712952</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.438733100891113</v>
+        <v>-6.276708126068115</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1184,43 +1184,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-79.23252868652344</v>
+        <v>-162.0289001464844</v>
       </c>
       <c r="B14" t="n">
-        <v>119.6492462158203</v>
+        <v>129.1089935302734</v>
       </c>
       <c r="C14" t="n">
-        <v>-23.7485408782959</v>
+        <v>-28.88247299194336</v>
       </c>
       <c r="D14" t="n">
-        <v>24.84591484069824</v>
+        <v>25.26452255249023</v>
       </c>
       <c r="E14" t="n">
-        <v>3.898741722106934</v>
+        <v>-1.407941222190857</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.84067535400391</v>
+        <v>-12.49144172668457</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.225146293640137</v>
+        <v>-2.153493404388428</v>
       </c>
       <c r="H14" t="n">
-        <v>-17.81306838989258</v>
+        <v>-14.36000823974609</v>
       </c>
       <c r="I14" t="n">
-        <v>8.971433639526367</v>
+        <v>7.334091186523438</v>
       </c>
       <c r="J14" t="n">
-        <v>5.528022766113281</v>
+        <v>4.68344783782959</v>
       </c>
       <c r="K14" t="n">
-        <v>6.218060970306396</v>
+        <v>6.456921577453613</v>
       </c>
       <c r="L14" t="n">
-        <v>3.798705101013184</v>
+        <v>1.770092368125916</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.11622142791748</v>
+        <v>-8.664896011352539</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1240,43 +1240,43 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-55.82753753662109</v>
+        <v>-137.2573089599609</v>
       </c>
       <c r="B15" t="n">
-        <v>147.913330078125</v>
+        <v>145.9951171875</v>
       </c>
       <c r="C15" t="n">
-        <v>-47.88676452636719</v>
+        <v>-45.61428070068359</v>
       </c>
       <c r="D15" t="n">
-        <v>28.74621200561523</v>
+        <v>28.34197044372559</v>
       </c>
       <c r="E15" t="n">
-        <v>-20.7788200378418</v>
+        <v>-18.54502487182617</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.838300228118896</v>
+        <v>-6.914748191833496</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.975383281707764</v>
+        <v>-6.276551246643066</v>
       </c>
       <c r="H15" t="n">
-        <v>-19.19586944580078</v>
+        <v>-19.87737083435059</v>
       </c>
       <c r="I15" t="n">
-        <v>10.38313102722168</v>
+        <v>6.820272922515869</v>
       </c>
       <c r="J15" t="n">
-        <v>5.996101856231689</v>
+        <v>3.413719654083252</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6702079772949219</v>
+        <v>1.550315976142883</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.930113315582275</v>
+        <v>-5.040169715881348</v>
       </c>
       <c r="M15" t="n">
-        <v>-14.33584117889404</v>
+        <v>-12.5319881439209</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1296,43 +1296,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-34.40943145751953</v>
+        <v>-123.3946151733398</v>
       </c>
       <c r="B16" t="n">
-        <v>125.461311340332</v>
+        <v>131.3920135498047</v>
       </c>
       <c r="C16" t="n">
-        <v>-33.67449951171875</v>
+        <v>-36.87621307373047</v>
       </c>
       <c r="D16" t="n">
-        <v>24.15680885314941</v>
+        <v>23.44138145446777</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.128495216369629</v>
+        <v>-10.03947639465332</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.92547225952148</v>
+        <v>-14.23273468017578</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.314825296401978</v>
+        <v>-1.762871980667114</v>
       </c>
       <c r="H16" t="n">
-        <v>-21.55322265625</v>
+        <v>-20.44469833374023</v>
       </c>
       <c r="I16" t="n">
-        <v>3.605244636535645</v>
+        <v>2.801754474639893</v>
       </c>
       <c r="J16" t="n">
-        <v>1.442545294761658</v>
+        <v>0.5960338711738586</v>
       </c>
       <c r="K16" t="n">
-        <v>5.970919132232666</v>
+        <v>4.799246788024902</v>
       </c>
       <c r="L16" t="n">
-        <v>2.81083607673645</v>
+        <v>2.8185715675354</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.476496696472168</v>
+        <v>-6.335023403167725</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1352,43 +1352,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-6.993817329406738</v>
+        <v>-104.9228286743164</v>
       </c>
       <c r="B17" t="n">
-        <v>108.9065246582031</v>
+        <v>122.2376327514648</v>
       </c>
       <c r="C17" t="n">
-        <v>-36.20023727416992</v>
+        <v>-41.24703216552734</v>
       </c>
       <c r="D17" t="n">
-        <v>24.03220558166504</v>
+        <v>21.51485061645508</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.378757476806641</v>
+        <v>-5.600813865661621</v>
       </c>
       <c r="F17" t="n">
-        <v>-23.05855941772461</v>
+        <v>-16.89181518554688</v>
       </c>
       <c r="G17" t="n">
-        <v>7.994312286376953</v>
+        <v>4.034528732299805</v>
       </c>
       <c r="H17" t="n">
-        <v>-18.47238731384277</v>
+        <v>-14.91325187683105</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4232478141784668</v>
+        <v>2.052506923675537</v>
       </c>
       <c r="J17" t="n">
-        <v>10.04016304016113</v>
+        <v>8.203325271606445</v>
       </c>
       <c r="K17" t="n">
-        <v>1.756926536560059</v>
+        <v>-0.9145110845565796</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8715844750404358</v>
+        <v>0.09261540323495865</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.979316234588623</v>
+        <v>-4.853033065795898</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1408,43 +1408,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-9.081676483154297</v>
+        <v>-107.2007904052734</v>
       </c>
       <c r="B18" t="n">
-        <v>111.7480926513672</v>
+        <v>123.9589004516602</v>
       </c>
       <c r="C18" t="n">
-        <v>-41.68596649169922</v>
+        <v>-44.71015548706055</v>
       </c>
       <c r="D18" t="n">
-        <v>33.51227569580078</v>
+        <v>30.70882797241211</v>
       </c>
       <c r="E18" t="n">
-        <v>-19.05681610107422</v>
+        <v>-14.61649131774902</v>
       </c>
       <c r="F18" t="n">
-        <v>-19.36031341552734</v>
+        <v>-15.99080371856689</v>
       </c>
       <c r="G18" t="n">
-        <v>7.203810691833496</v>
+        <v>2.919788122177124</v>
       </c>
       <c r="H18" t="n">
-        <v>-26.93455123901367</v>
+        <v>-21.77852249145508</v>
       </c>
       <c r="I18" t="n">
-        <v>6.800590515136719</v>
+        <v>6.427609443664551</v>
       </c>
       <c r="J18" t="n">
-        <v>2.425358533859253</v>
+        <v>1.34154200553894</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.798908233642578</v>
+        <v>-6.900435447692871</v>
       </c>
       <c r="L18" t="n">
-        <v>3.931180477142334</v>
+        <v>2.560858249664307</v>
       </c>
       <c r="M18" t="n">
-        <v>-13.00066947937012</v>
+        <v>-9.519834518432617</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1464,43 +1464,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-47.94475173950195</v>
+        <v>-128.2447662353516</v>
       </c>
       <c r="B19" t="n">
-        <v>146.1143341064453</v>
+        <v>146.1290588378906</v>
       </c>
       <c r="C19" t="n">
-        <v>-44.40506744384766</v>
+        <v>-47.17734527587891</v>
       </c>
       <c r="D19" t="n">
-        <v>28.46457862854004</v>
+        <v>27.36420631408691</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.08392524719238</v>
+        <v>-11.88662242889404</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.94735145568848</v>
+        <v>-11.91369438171387</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3538424968719482</v>
+        <v>-1.47430419921875</v>
       </c>
       <c r="H19" t="n">
-        <v>-12.44918823242188</v>
+        <v>-12.16908740997314</v>
       </c>
       <c r="I19" t="n">
-        <v>5.219233512878418</v>
+        <v>6.201236248016357</v>
       </c>
       <c r="J19" t="n">
-        <v>6.861628532409668</v>
+        <v>3.461521863937378</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3248788118362427</v>
+        <v>0.3517950475215912</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.199848175048828</v>
+        <v>-1.281276941299438</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.561396598815918</v>
+        <v>-2.02388858795166</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1520,43 +1520,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-47.77490615844727</v>
+        <v>-130.1510162353516</v>
       </c>
       <c r="B20" t="n">
-        <v>145.2520599365234</v>
+        <v>146.9816436767578</v>
       </c>
       <c r="C20" t="n">
-        <v>-45.95113372802734</v>
+        <v>-46.74148941040039</v>
       </c>
       <c r="D20" t="n">
-        <v>23.07193756103516</v>
+        <v>24.74489784240723</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.738007545471191</v>
+        <v>-4.962358951568604</v>
       </c>
       <c r="F20" t="n">
-        <v>-16.92867088317871</v>
+        <v>-16.35575866699219</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.303942680358887</v>
+        <v>-4.369231224060059</v>
       </c>
       <c r="H20" t="n">
-        <v>-15.76884651184082</v>
+        <v>-16.44231224060059</v>
       </c>
       <c r="I20" t="n">
-        <v>7.12506103515625</v>
+        <v>4.828499794006348</v>
       </c>
       <c r="J20" t="n">
-        <v>4.324636936187744</v>
+        <v>0.04307328537106514</v>
       </c>
       <c r="K20" t="n">
-        <v>5.583824157714844</v>
+        <v>4.477180480957031</v>
       </c>
       <c r="L20" t="n">
-        <v>1.403789043426514</v>
+        <v>3.824455976486206</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.889609336853027</v>
+        <v>-1.511861085891724</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1576,43 +1576,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-27.54493141174316</v>
+        <v>-132.6946716308594</v>
       </c>
       <c r="B21" t="n">
-        <v>107.6512298583984</v>
+        <v>126.2445678710938</v>
       </c>
       <c r="C21" t="n">
-        <v>-27.08330154418945</v>
+        <v>-33.10166931152344</v>
       </c>
       <c r="D21" t="n">
-        <v>30.29557609558105</v>
+        <v>27.06007385253906</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.876189231872559</v>
+        <v>-2.086511135101318</v>
       </c>
       <c r="F21" t="n">
-        <v>-19.67034149169922</v>
+        <v>-19.76446533203125</v>
       </c>
       <c r="G21" t="n">
-        <v>5.259865760803223</v>
+        <v>-1.230315446853638</v>
       </c>
       <c r="H21" t="n">
-        <v>-16.13751411437988</v>
+        <v>-14.19471549987793</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.51975154876709</v>
+        <v>2.722138404846191</v>
       </c>
       <c r="J21" t="n">
-        <v>4.40333366394043</v>
+        <v>0.2205419540405273</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.193296909332275</v>
+        <v>-3.343476533889771</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.939731597900391</v>
+        <v>-2.734405279159546</v>
       </c>
       <c r="M21" t="n">
-        <v>-8.13447380065918</v>
+        <v>-5.327744960784912</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1632,43 +1632,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-20.38778686523438</v>
+        <v>-114.3089218139648</v>
       </c>
       <c r="B22" t="n">
-        <v>123.7190017700195</v>
+        <v>141.8971557617188</v>
       </c>
       <c r="C22" t="n">
-        <v>-15.45013523101807</v>
+        <v>-19.27654457092285</v>
       </c>
       <c r="D22" t="n">
-        <v>22.37673950195312</v>
+        <v>23.78809547424316</v>
       </c>
       <c r="E22" t="n">
-        <v>-22.64885520935059</v>
+        <v>-21.64617538452148</v>
       </c>
       <c r="F22" t="n">
-        <v>1.150037050247192</v>
+        <v>-0.1219220161437988</v>
       </c>
       <c r="G22" t="n">
-        <v>14.48337936401367</v>
+        <v>10.07266712188721</v>
       </c>
       <c r="H22" t="n">
-        <v>-11.15673828125</v>
+        <v>-13.41169929504395</v>
       </c>
       <c r="I22" t="n">
-        <v>4.912160873413086</v>
+        <v>6.889441013336182</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6678223609924316</v>
+        <v>-5.26823902130127</v>
       </c>
       <c r="K22" t="n">
-        <v>4.809696197509766</v>
+        <v>5.200957775115967</v>
       </c>
       <c r="L22" t="n">
-        <v>16.63393402099609</v>
+        <v>8.211919784545898</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1311541795730591</v>
+        <v>-0.4944759011268616</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1688,43 +1688,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>59.64924621582031</v>
+        <v>-54.71331024169922</v>
       </c>
       <c r="B23" t="n">
-        <v>63.71730041503906</v>
+        <v>109.1549530029297</v>
       </c>
       <c r="C23" t="n">
-        <v>-9.453037261962891</v>
+        <v>-23.96333694458008</v>
       </c>
       <c r="D23" t="n">
-        <v>16.25179672241211</v>
+        <v>9.936526298522949</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.258745193481445</v>
+        <v>-16.36203956604004</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6988469362258911</v>
+        <v>-0.5628713965415955</v>
       </c>
       <c r="G23" t="n">
-        <v>12.63141632080078</v>
+        <v>11.47879791259766</v>
       </c>
       <c r="H23" t="n">
-        <v>-8.698083877563477</v>
+        <v>-14.48255920410156</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.05882453918457</v>
+        <v>1.67756974697113</v>
       </c>
       <c r="J23" t="n">
-        <v>4.653767585754395</v>
+        <v>4.247185707092285</v>
       </c>
       <c r="K23" t="n">
-        <v>4.478461265563965</v>
+        <v>5.548502922058105</v>
       </c>
       <c r="L23" t="n">
-        <v>7.599067687988281</v>
+        <v>5.85704517364502</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.336525917053223</v>
+        <v>-9.136754989624023</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1744,43 +1744,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>81.9110107421875</v>
+        <v>-23.00691032409668</v>
       </c>
       <c r="B24" t="n">
-        <v>58.14257049560547</v>
+        <v>91.93797302246094</v>
       </c>
       <c r="C24" t="n">
-        <v>-11.93302154541016</v>
+        <v>-15.07370948791504</v>
       </c>
       <c r="D24" t="n">
-        <v>11.94034290313721</v>
+        <v>10.6143045425415</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.179166793823242</v>
+        <v>-15.43610572814941</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.563315391540527</v>
+        <v>-5.707858085632324</v>
       </c>
       <c r="G24" t="n">
-        <v>3.054642915725708</v>
+        <v>4.800432205200195</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.924272060394287</v>
+        <v>-9.787860870361328</v>
       </c>
       <c r="I24" t="n">
-        <v>1.986850023269653</v>
+        <v>2.031813144683838</v>
       </c>
       <c r="J24" t="n">
-        <v>5.170926570892334</v>
+        <v>0.8644777536392212</v>
       </c>
       <c r="K24" t="n">
-        <v>2.812670469284058</v>
+        <v>8.705926895141602</v>
       </c>
       <c r="L24" t="n">
-        <v>4.453874588012695</v>
+        <v>2.073014497756958</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.136713027954102</v>
+        <v>-6.261673927307129</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1800,43 +1800,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5.724708557128906</v>
+        <v>-112.7874526977539</v>
       </c>
       <c r="B25" t="n">
-        <v>69.66585540771484</v>
+        <v>105.1566009521484</v>
       </c>
       <c r="C25" t="n">
-        <v>-5.289958953857422</v>
+        <v>-11.59104061126709</v>
       </c>
       <c r="D25" t="n">
-        <v>21.78210830688477</v>
+        <v>23.22334671020508</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.24944877624512</v>
+        <v>-17.66128921508789</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.939773082733154</v>
+        <v>-1.766091108322144</v>
       </c>
       <c r="G25" t="n">
-        <v>8.614442825317383</v>
+        <v>7.164726257324219</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.361204147338867</v>
+        <v>-8.518514633178711</v>
       </c>
       <c r="I25" t="n">
-        <v>8.281285285949707</v>
+        <v>10.56892967224121</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.925089359283447</v>
+        <v>-6.978455543518066</v>
       </c>
       <c r="K25" t="n">
-        <v>0.734304666519165</v>
+        <v>7.948988437652588</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.189141035079956</v>
+        <v>-2.323215007781982</v>
       </c>
       <c r="M25" t="n">
-        <v>10.00070762634277</v>
+        <v>6.836075782775879</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1856,43 +1856,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>88.25578308105469</v>
+        <v>-21.6891040802002</v>
       </c>
       <c r="B26" t="n">
-        <v>57.50599670410156</v>
+        <v>97.94419860839844</v>
       </c>
       <c r="C26" t="n">
-        <v>-9.737007141113281</v>
+        <v>-22.51995086669922</v>
       </c>
       <c r="D26" t="n">
-        <v>5.279827117919922</v>
+        <v>2.349121570587158</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.31373405456543</v>
+        <v>-11.03468990325928</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.414810657501221</v>
+        <v>-5.04388427734375</v>
       </c>
       <c r="G26" t="n">
-        <v>18.22062683105469</v>
+        <v>19.13506698608398</v>
       </c>
       <c r="H26" t="n">
-        <v>-14.10189723968506</v>
+        <v>-17.45739364624023</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4736920595169067</v>
+        <v>2.598029613494873</v>
       </c>
       <c r="J26" t="n">
-        <v>3.454010725021362</v>
+        <v>7.15006160736084</v>
       </c>
       <c r="K26" t="n">
-        <v>3.362349033355713</v>
+        <v>7.45037841796875</v>
       </c>
       <c r="L26" t="n">
-        <v>1.270719051361084</v>
+        <v>-1.455288171768188</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.611547470092773</v>
+        <v>-9.544145584106445</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1912,43 +1912,43 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>69.98244476318359</v>
+        <v>-39.29498291015625</v>
       </c>
       <c r="B27" t="n">
-        <v>68.96781921386719</v>
+        <v>96.51728820800781</v>
       </c>
       <c r="C27" t="n">
-        <v>-11.50281810760498</v>
+        <v>-19.3630256652832</v>
       </c>
       <c r="D27" t="n">
-        <v>14.05529022216797</v>
+        <v>12.42712688446045</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.916312217712402</v>
+        <v>-12.5396556854248</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6288943290710449</v>
+        <v>1.423182368278503</v>
       </c>
       <c r="G27" t="n">
-        <v>15.61032676696777</v>
+        <v>15.76641654968262</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.027802467346191</v>
+        <v>-11.1890926361084</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.528444409370422</v>
+        <v>2.757111549377441</v>
       </c>
       <c r="J27" t="n">
-        <v>8.973652839660645</v>
+        <v>6.39623498916626</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5921351313591003</v>
+        <v>7.209391117095947</v>
       </c>
       <c r="L27" t="n">
-        <v>3.59762716293335</v>
+        <v>1.383382558822632</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.190004348754883</v>
+        <v>-1.926021575927734</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1968,43 +1968,43 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>74.13119506835938</v>
+        <v>-64.50688171386719</v>
       </c>
       <c r="B28" t="n">
-        <v>64.00780487060547</v>
+        <v>94.98991394042969</v>
       </c>
       <c r="C28" t="n">
-        <v>-17.73674583435059</v>
+        <v>-21.73426055908203</v>
       </c>
       <c r="D28" t="n">
-        <v>17.59664535522461</v>
+        <v>16.33814811706543</v>
       </c>
       <c r="E28" t="n">
-        <v>-10.39289283752441</v>
+        <v>-6.790799140930176</v>
       </c>
       <c r="F28" t="n">
-        <v>3.011325359344482</v>
+        <v>2.283556938171387</v>
       </c>
       <c r="G28" t="n">
-        <v>7.9043869972229</v>
+        <v>6.895432949066162</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.559561729431152</v>
+        <v>-10.45977306365967</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2081146240234375</v>
+        <v>2.071388244628906</v>
       </c>
       <c r="J28" t="n">
-        <v>5.572865962982178</v>
+        <v>4.222843170166016</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7636615633964539</v>
+        <v>5.156745433807373</v>
       </c>
       <c r="L28" t="n">
-        <v>6.170965671539307</v>
+        <v>1.611684441566467</v>
       </c>
       <c r="M28" t="n">
-        <v>-4.252102375030518</v>
+        <v>-6.135851383209229</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2024,43 +2024,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-51.1192626953125</v>
+        <v>-149.6282043457031</v>
       </c>
       <c r="B29" t="n">
-        <v>117.3904418945312</v>
+        <v>135.0574645996094</v>
       </c>
       <c r="C29" t="n">
-        <v>-30.40019226074219</v>
+        <v>-31.75507736206055</v>
       </c>
       <c r="D29" t="n">
-        <v>22.74531173706055</v>
+        <v>19.91539192199707</v>
       </c>
       <c r="E29" t="n">
-        <v>-14.70256805419922</v>
+        <v>-12.88830280303955</v>
       </c>
       <c r="F29" t="n">
-        <v>-6.621948719024658</v>
+        <v>-7.423638820648193</v>
       </c>
       <c r="G29" t="n">
-        <v>10.52336311340332</v>
+        <v>4.16274881362915</v>
       </c>
       <c r="H29" t="n">
-        <v>-17.26933670043945</v>
+        <v>-12.35912322998047</v>
       </c>
       <c r="I29" t="n">
-        <v>15.78891468048096</v>
+        <v>14.86945629119873</v>
       </c>
       <c r="J29" t="n">
-        <v>7.230295181274414</v>
+        <v>4.651859283447266</v>
       </c>
       <c r="K29" t="n">
-        <v>4.03924036026001</v>
+        <v>2.26069712638855</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.767011642456055</v>
+        <v>-3.786916732788086</v>
       </c>
       <c r="M29" t="n">
-        <v>2.412254333496094</v>
+        <v>1.676132798194885</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2080,43 +2080,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>86.50965881347656</v>
+        <v>-22.54913520812988</v>
       </c>
       <c r="B30" t="n">
-        <v>62.87178421020508</v>
+        <v>99.79698181152344</v>
       </c>
       <c r="C30" t="n">
-        <v>-12.98698329925537</v>
+        <v>-22.36599349975586</v>
       </c>
       <c r="D30" t="n">
-        <v>14.75119495391846</v>
+        <v>10.69077014923096</v>
       </c>
       <c r="E30" t="n">
-        <v>-14.73324298858643</v>
+        <v>-22.94460678100586</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.8880600929260254</v>
+        <v>-2.577513694763184</v>
       </c>
       <c r="G30" t="n">
-        <v>9.016440391540527</v>
+        <v>12.94677925109863</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.23507881164551</v>
+        <v>-17.95139694213867</v>
       </c>
       <c r="I30" t="n">
-        <v>1.289515614509583</v>
+        <v>4.636207103729248</v>
       </c>
       <c r="J30" t="n">
-        <v>3.271676063537598</v>
+        <v>2.192812919616699</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.424529194831848</v>
+        <v>1.140582203865051</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5591740608215332</v>
+        <v>1.422171354293823</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.191425323486328</v>
+        <v>-5.296605110168457</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2136,43 +2136,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-23.06859970092773</v>
+        <v>-110.3166046142578</v>
       </c>
       <c r="B31" t="n">
-        <v>137.9472045898438</v>
+        <v>152.4229888916016</v>
       </c>
       <c r="C31" t="n">
-        <v>-26.18479156494141</v>
+        <v>-30.45219993591309</v>
       </c>
       <c r="D31" t="n">
-        <v>22.01977157592773</v>
+        <v>19.98880195617676</v>
       </c>
       <c r="E31" t="n">
-        <v>-18.64120483398438</v>
+        <v>-20.74697303771973</v>
       </c>
       <c r="F31" t="n">
-        <v>2.045474052429199</v>
+        <v>-0.4330118596553802</v>
       </c>
       <c r="G31" t="n">
-        <v>13.34281158447266</v>
+        <v>11.57272052764893</v>
       </c>
       <c r="H31" t="n">
-        <v>-9.355486869812012</v>
+        <v>-10.97251319885254</v>
       </c>
       <c r="I31" t="n">
-        <v>5.80120849609375</v>
+        <v>8.163460731506348</v>
       </c>
       <c r="J31" t="n">
-        <v>3.232617855072021</v>
+        <v>2.647861957550049</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.3744091391563416</v>
+        <v>3.260255098342896</v>
       </c>
       <c r="L31" t="n">
-        <v>3.470405340194702</v>
+        <v>2.83936882019043</v>
       </c>
       <c r="M31" t="n">
-        <v>1.964379668235779</v>
+        <v>0.1663976907730103</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2192,43 +2192,43 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-38.81666946411133</v>
+        <v>-130.4892425537109</v>
       </c>
       <c r="B32" t="n">
-        <v>144.4555358886719</v>
+        <v>143.7386932373047</v>
       </c>
       <c r="C32" t="n">
-        <v>-36.67446899414062</v>
+        <v>-33.29931640625</v>
       </c>
       <c r="D32" t="n">
-        <v>37.58754730224609</v>
+        <v>39.41465377807617</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.609708309173584</v>
+        <v>-2.449430704116821</v>
       </c>
       <c r="F32" t="n">
-        <v>-21.82903671264648</v>
+        <v>-15.34087371826172</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3819043636322021</v>
+        <v>1.217504739761353</v>
       </c>
       <c r="H32" t="n">
-        <v>-10.09470748901367</v>
+        <v>-11.09848117828369</v>
       </c>
       <c r="I32" t="n">
-        <v>9.164710998535156</v>
+        <v>9.626367568969727</v>
       </c>
       <c r="J32" t="n">
-        <v>9.678985595703125</v>
+        <v>7.228171348571777</v>
       </c>
       <c r="K32" t="n">
-        <v>-10.30873966217041</v>
+        <v>-7.095694541931152</v>
       </c>
       <c r="L32" t="n">
-        <v>-6.561491966247559</v>
+        <v>-5.384739875793457</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.246865749359131</v>
+        <v>-4.556272506713867</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2248,43 +2248,43 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-59.96945571899414</v>
+        <v>-140.8003997802734</v>
       </c>
       <c r="B33" t="n">
-        <v>149.7138671875</v>
+        <v>144.3470764160156</v>
       </c>
       <c r="C33" t="n">
-        <v>-27.4206714630127</v>
+        <v>-25.66958236694336</v>
       </c>
       <c r="D33" t="n">
-        <v>27.07188606262207</v>
+        <v>28.15273094177246</v>
       </c>
       <c r="E33" t="n">
-        <v>12.03425979614258</v>
+        <v>10.06859874725342</v>
       </c>
       <c r="F33" t="n">
-        <v>-22.39077377319336</v>
+        <v>-20.46837997436523</v>
       </c>
       <c r="G33" t="n">
-        <v>1.191161394119263</v>
+        <v>-2.026472568511963</v>
       </c>
       <c r="H33" t="n">
-        <v>-8.85800838470459</v>
+        <v>-9.876206398010254</v>
       </c>
       <c r="I33" t="n">
-        <v>13.44608688354492</v>
+        <v>12.66718006134033</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1116341352462769</v>
+        <v>0.2817770540714264</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.43355369567871</v>
+        <v>-8.856178283691406</v>
       </c>
       <c r="L33" t="n">
-        <v>-4.635310649871826</v>
+        <v>-1.805980086326599</v>
       </c>
       <c r="M33" t="n">
-        <v>-8.691716194152832</v>
+        <v>-9.221311569213867</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2304,43 +2304,43 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-10.28546333312988</v>
+        <v>-111.3262786865234</v>
       </c>
       <c r="B34" t="n">
-        <v>141.5125122070312</v>
+        <v>140.1288757324219</v>
       </c>
       <c r="C34" t="n">
-        <v>-31.33033752441406</v>
+        <v>-31.98380661010742</v>
       </c>
       <c r="D34" t="n">
-        <v>29.23284339904785</v>
+        <v>31.46829605102539</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.658007621765137</v>
+        <v>-2.380415439605713</v>
       </c>
       <c r="F34" t="n">
-        <v>-21.56808662414551</v>
+        <v>-16.36345672607422</v>
       </c>
       <c r="G34" t="n">
-        <v>2.317570209503174</v>
+        <v>2.822119474411011</v>
       </c>
       <c r="H34" t="n">
-        <v>-17.94597434997559</v>
+        <v>-17.87797164916992</v>
       </c>
       <c r="I34" t="n">
-        <v>21.48738479614258</v>
+        <v>20.51541519165039</v>
       </c>
       <c r="J34" t="n">
-        <v>1.767487049102783</v>
+        <v>1.842442870140076</v>
       </c>
       <c r="K34" t="n">
-        <v>-19.3849048614502</v>
+        <v>-13.72345447540283</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7288873195648193</v>
+        <v>-0.01314420718699694</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.387025356292725</v>
+        <v>-2.193950414657593</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2360,43 +2360,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-65.70687866210938</v>
+        <v>-150.2800140380859</v>
       </c>
       <c r="B35" t="n">
-        <v>153.6451568603516</v>
+        <v>146.4934387207031</v>
       </c>
       <c r="C35" t="n">
-        <v>-18.49061965942383</v>
+        <v>-17.68147277832031</v>
       </c>
       <c r="D35" t="n">
-        <v>30.66348266601562</v>
+        <v>31.11378860473633</v>
       </c>
       <c r="E35" t="n">
-        <v>1.563776612281799</v>
+        <v>3.667624950408936</v>
       </c>
       <c r="F35" t="n">
-        <v>-10.99791145324707</v>
+        <v>-8.580371856689453</v>
       </c>
       <c r="G35" t="n">
-        <v>-5.358700752258301</v>
+        <v>-4.799100875854492</v>
       </c>
       <c r="H35" t="n">
-        <v>-7.456603527069092</v>
+        <v>-5.250979900360107</v>
       </c>
       <c r="I35" t="n">
-        <v>16.07112884521484</v>
+        <v>14.34134197235107</v>
       </c>
       <c r="J35" t="n">
-        <v>2.323585748672485</v>
+        <v>1.895046234130859</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.439966678619385</v>
+        <v>-5.292319774627686</v>
       </c>
       <c r="L35" t="n">
-        <v>-5.729353427886963</v>
+        <v>-3.883633852005005</v>
       </c>
       <c r="M35" t="n">
-        <v>1.216680526733398</v>
+        <v>-1.191548824310303</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2416,43 +2416,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-32.6185417175293</v>
+        <v>-127.3816146850586</v>
       </c>
       <c r="B36" t="n">
-        <v>122.7339324951172</v>
+        <v>133.0901336669922</v>
       </c>
       <c r="C36" t="n">
-        <v>-29.69515037536621</v>
+        <v>-33.07709121704102</v>
       </c>
       <c r="D36" t="n">
-        <v>32.22972106933594</v>
+        <v>35.84734725952148</v>
       </c>
       <c r="E36" t="n">
-        <v>-9.453845024108887</v>
+        <v>-7.666586875915527</v>
       </c>
       <c r="F36" t="n">
-        <v>-5.141208648681641</v>
+        <v>-7.003993988037109</v>
       </c>
       <c r="G36" t="n">
-        <v>-4.584595680236816</v>
+        <v>-5.791198253631592</v>
       </c>
       <c r="H36" t="n">
-        <v>-21.86382293701172</v>
+        <v>-22.28780555725098</v>
       </c>
       <c r="I36" t="n">
-        <v>10.29101181030273</v>
+        <v>10.09733867645264</v>
       </c>
       <c r="J36" t="n">
-        <v>3.251049041748047</v>
+        <v>-1.110795855522156</v>
       </c>
       <c r="K36" t="n">
-        <v>-14.27432060241699</v>
+        <v>-7.676186561584473</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1205525398254395</v>
+        <v>-2.164419412612915</v>
       </c>
       <c r="M36" t="n">
-        <v>-8.163700103759766</v>
+        <v>-3.62864875793457</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2472,43 +2472,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-4.316352844238281</v>
+        <v>-106.77734375</v>
       </c>
       <c r="B37" t="n">
-        <v>87.53806304931641</v>
+        <v>108.9464569091797</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.913559317588806</v>
+        <v>-16.01902389526367</v>
       </c>
       <c r="D37" t="n">
-        <v>3.133590459823608</v>
+        <v>14.2483081817627</v>
       </c>
       <c r="E37" t="n">
-        <v>3.318132400512695</v>
+        <v>0.05665387958288193</v>
       </c>
       <c r="F37" t="n">
-        <v>-8.436339378356934</v>
+        <v>-7.43404483795166</v>
       </c>
       <c r="G37" t="n">
-        <v>-8.08600902557373</v>
+        <v>-3.171406030654907</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.350376844406128</v>
+        <v>-7.978720664978027</v>
       </c>
       <c r="I37" t="n">
-        <v>9.026849746704102</v>
+        <v>11.14952373504639</v>
       </c>
       <c r="J37" t="n">
-        <v>4.134526252746582</v>
+        <v>1.488881707191467</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.483448028564453</v>
+        <v>-5.670284748077393</v>
       </c>
       <c r="L37" t="n">
-        <v>-5.845293045043945</v>
+        <v>-4.966145038604736</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.310791969299316</v>
+        <v>-3.179202556610107</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2528,43 +2528,43 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-43.68737411499023</v>
+        <v>-138.2424926757812</v>
       </c>
       <c r="B38" t="n">
-        <v>134.5790557861328</v>
+        <v>137.6624145507812</v>
       </c>
       <c r="C38" t="n">
-        <v>-25.65071678161621</v>
+        <v>-26.61909866333008</v>
       </c>
       <c r="D38" t="n">
-        <v>29.69024658203125</v>
+        <v>30.44736289978027</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8249391317367554</v>
+        <v>-4.277061939239502</v>
       </c>
       <c r="F38" t="n">
-        <v>-12.54806995391846</v>
+        <v>-8.441255569458008</v>
       </c>
       <c r="G38" t="n">
-        <v>10.16463661193848</v>
+        <v>9.533779144287109</v>
       </c>
       <c r="H38" t="n">
-        <v>-7.455234527587891</v>
+        <v>-6.932821750640869</v>
       </c>
       <c r="I38" t="n">
-        <v>6.80546760559082</v>
+        <v>6.394657135009766</v>
       </c>
       <c r="J38" t="n">
-        <v>2.297531843185425</v>
+        <v>0.7399020195007324</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.865301370620728</v>
+        <v>-2.265281438827515</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.468611717224121</v>
+        <v>-2.609048843383789</v>
       </c>
       <c r="M38" t="n">
-        <v>-4.237308979034424</v>
+        <v>-4.915671348571777</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2584,43 +2584,43 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-11.40614318847656</v>
+        <v>-109.3854370117188</v>
       </c>
       <c r="B39" t="n">
-        <v>148.4408264160156</v>
+        <v>145.9344787597656</v>
       </c>
       <c r="C39" t="n">
-        <v>-39.38896179199219</v>
+        <v>-42.69928359985352</v>
       </c>
       <c r="D39" t="n">
-        <v>25.33176422119141</v>
+        <v>30.20314598083496</v>
       </c>
       <c r="E39" t="n">
-        <v>-13.31790351867676</v>
+        <v>-12.63897323608398</v>
       </c>
       <c r="F39" t="n">
-        <v>-15.88465881347656</v>
+        <v>-9.526317596435547</v>
       </c>
       <c r="G39" t="n">
-        <v>8.46068000793457</v>
+        <v>6.816973209381104</v>
       </c>
       <c r="H39" t="n">
-        <v>-10.27483940124512</v>
+        <v>-8.116127967834473</v>
       </c>
       <c r="I39" t="n">
-        <v>9.024722099304199</v>
+        <v>11.2170238494873</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.581375122070312</v>
+        <v>-5.331121921539307</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.85817813873291</v>
+        <v>-6.345210075378418</v>
       </c>
       <c r="L39" t="n">
-        <v>-6.436631202697754</v>
+        <v>-5.554867267608643</v>
       </c>
       <c r="M39" t="n">
-        <v>-8.631892204284668</v>
+        <v>-9.259806632995605</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2640,43 +2640,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-83.86772155761719</v>
+        <v>-164.1865997314453</v>
       </c>
       <c r="B40" t="n">
-        <v>142.6986541748047</v>
+        <v>137.5317993164062</v>
       </c>
       <c r="C40" t="n">
-        <v>-33.02392196655273</v>
+        <v>-30.11039733886719</v>
       </c>
       <c r="D40" t="n">
-        <v>31.7792911529541</v>
+        <v>28.74190139770508</v>
       </c>
       <c r="E40" t="n">
-        <v>-16.46760940551758</v>
+        <v>-9.985692024230957</v>
       </c>
       <c r="F40" t="n">
-        <v>-4.379992008209229</v>
+        <v>-4.768794059753418</v>
       </c>
       <c r="G40" t="n">
-        <v>10.87947082519531</v>
+        <v>5.387024879455566</v>
       </c>
       <c r="H40" t="n">
-        <v>-16.77433013916016</v>
+        <v>-15.85017967224121</v>
       </c>
       <c r="I40" t="n">
-        <v>16.44384002685547</v>
+        <v>12.38315010070801</v>
       </c>
       <c r="J40" t="n">
-        <v>5.333250522613525</v>
+        <v>4.590596675872803</v>
       </c>
       <c r="K40" t="n">
-        <v>-7.747468948364258</v>
+        <v>-3.866965055465698</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.792082786560059</v>
+        <v>-5.143880844116211</v>
       </c>
       <c r="M40" t="n">
-        <v>-6.986350536346436</v>
+        <v>-5.380993366241455</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -2696,43 +2696,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-56.05964660644531</v>
+        <v>-133.9985046386719</v>
       </c>
       <c r="B41" t="n">
-        <v>134.0142517089844</v>
+        <v>129.6832580566406</v>
       </c>
       <c r="C41" t="n">
-        <v>-38.56221008300781</v>
+        <v>-38.19620513916016</v>
       </c>
       <c r="D41" t="n">
-        <v>23.0645751953125</v>
+        <v>21.27714157104492</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.451848983764648</v>
+        <v>-6.534412384033203</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.750684261322021</v>
+        <v>-0.2349912226200104</v>
       </c>
       <c r="G41" t="n">
-        <v>9.574556350708008</v>
+        <v>7.356008052825928</v>
       </c>
       <c r="H41" t="n">
-        <v>-19.94680786132812</v>
+        <v>-18.29620742797852</v>
       </c>
       <c r="I41" t="n">
-        <v>3.624521970748901</v>
+        <v>2.113290071487427</v>
       </c>
       <c r="J41" t="n">
-        <v>4.395712375640869</v>
+        <v>0.1065125912427902</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.062682151794434</v>
+        <v>-4.050545215606689</v>
       </c>
       <c r="L41" t="n">
-        <v>-5.979804515838623</v>
+        <v>-3.579590559005737</v>
       </c>
       <c r="M41" t="n">
-        <v>-5.002154350280762</v>
+        <v>-5.067817687988281</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2747,6 +2747,566 @@
       <c r="P41" t="inlineStr">
         <is>
           <t>Joel</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>-247.1817169189453</v>
+      </c>
+      <c r="B42" t="n">
+        <v>125.1184692382812</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-3.404644012451172</v>
+      </c>
+      <c r="D42" t="n">
+        <v>34.0421257019043</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4.472271919250488</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-17.9625244140625</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-4.488899230957031</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-14.84111309051514</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.547022581100464</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-3.872407197952271</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-1.033003211021423</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-1.0645512342453</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-3.71502161026001</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Noise0.wav</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>-235.3594360351562</v>
+      </c>
+      <c r="B43" t="n">
+        <v>119.4857406616211</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-15.93755531311035</v>
+      </c>
+      <c r="D43" t="n">
+        <v>30.8370418548584</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.402406215667725</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-10.39338779449463</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-2.412044048309326</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-13.33867835998535</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.079801321029663</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-1.900209784507751</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.628575325012207</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-0.7113485932350159</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-3.123025178909302</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Noise1.wav</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>-212.04345703125</v>
+      </c>
+      <c r="B44" t="n">
+        <v>122.1678237915039</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-22.29970169067383</v>
+      </c>
+      <c r="D44" t="n">
+        <v>24.76311874389648</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-8.315286636352539</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-14.28957462310791</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-7.446599006652832</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-17.1152515411377</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5.832901477813721</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-3.249933242797852</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5.406060695648193</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.6451848149299622</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-1.453296303749084</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Noise2.wav</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>-221.6649169921875</v>
+      </c>
+      <c r="B45" t="n">
+        <v>123.0949401855469</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-18.94107627868652</v>
+      </c>
+      <c r="D45" t="n">
+        <v>27.77348136901855</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-12.99815940856934</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-10.08580780029297</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.860066652297974</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-13.18554782867432</v>
+      </c>
+      <c r="I45" t="n">
+        <v>6.866611480712891</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-5.436584949493408</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.249138116836548</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-1.97796642780304</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-3.153973340988159</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Noise3.wav</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>-191.7421264648438</v>
+      </c>
+      <c r="B46" t="n">
+        <v>136.0635833740234</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-23.05634307861328</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6.333216667175293</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-14.7941951751709</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-1.10232138633728</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-1.429682612419128</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-25.35762786865234</v>
+      </c>
+      <c r="I46" t="n">
+        <v>7.486058235168457</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.975748538970947</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-2.980402708053589</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-4.275497913360596</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-3.905026435852051</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Noise4.wav</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>-212.5359344482422</v>
+      </c>
+      <c r="B47" t="n">
+        <v>125.1713485717773</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-29.95211029052734</v>
+      </c>
+      <c r="D47" t="n">
+        <v>25.37268447875977</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-3.565201282501221</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-10.36992168426514</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-4.683012008666992</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-14.86567401885986</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.686466336250305</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.2993330955505371</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.609511852264404</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.35072386264801</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-1.134132623672485</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Noise5.wav</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>-197.9402618408203</v>
+      </c>
+      <c r="B48" t="n">
+        <v>124.6808700561523</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-18.39752197265625</v>
+      </c>
+      <c r="D48" t="n">
+        <v>21.85722351074219</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-8.142490386962891</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-8.642642021179199</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-1.446395754814148</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-16.30740928649902</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4.098618984222412</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-1.522964596748352</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.172059535980225</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.615381717681885</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-1.582821488380432</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Noise6.wav</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>-186.2667541503906</v>
+      </c>
+      <c r="B49" t="n">
+        <v>118.1522598266602</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-21.46571922302246</v>
+      </c>
+      <c r="D49" t="n">
+        <v>24.74458694458008</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-7.955282211303711</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-13.60531425476074</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-5.72638463973999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-14.20610332489014</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.129168033599854</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-1.708194375038147</v>
+      </c>
+      <c r="K49" t="n">
+        <v>6.451208114624023</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-3.536592483520508</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-4.601926326751709</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Noise7.wav</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>-207.0384826660156</v>
+      </c>
+      <c r="B50" t="n">
+        <v>122.6781921386719</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-18.23495101928711</v>
+      </c>
+      <c r="D50" t="n">
+        <v>28.73486328125</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-4.844429016113281</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-8.085786819458008</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-3.434430599212646</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-10.9806547164917</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5.260439872741699</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-4.370806694030762</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.7166019678115845</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-1.101075053215027</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-4.173426628112793</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Noise8.wav</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>-216.7819366455078</v>
+      </c>
+      <c r="B51" t="n">
+        <v>115.4441833496094</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-15.67872333526611</v>
+      </c>
+      <c r="D51" t="n">
+        <v>28.75668334960938</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-4.685660362243652</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-6.137412548065186</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-1.738136529922485</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-23.67157363891602</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3.502881526947021</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.063827276229858</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5.36333179473877</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-2.103987693786621</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-1.587156295776367</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Noise9.wav</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>NOISE</t>
         </is>
       </c>
     </row>
